--- a/SRC/Controller/HVAC_controller/State_Reward_action defintion.xlsx
+++ b/SRC/Controller/HVAC_controller/State_Reward_action defintion.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YajuR\Desktop\Autonomy\Dwelling_simulator\SRC\Controller\HVAC_controller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E908403D-645D-435D-AD64-E5255228F5CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC64148-1E05-4B38-BF2A-2F2E68A0D8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2F0CEAD1-91A2-44EE-9519-226D71FD8C97}"/>
   </bookViews>
   <sheets>
     <sheet name="Reward" sheetId="1" r:id="rId1"/>
     <sheet name="Reward Type 3" sheetId="3" r:id="rId2"/>
-    <sheet name="Reward Type 2" sheetId="4" r:id="rId3"/>
-    <sheet name="Rate change" sheetId="2" r:id="rId4"/>
-    <sheet name="Boundary " sheetId="5" r:id="rId5"/>
+    <sheet name="Reward Type 4" sheetId="6" r:id="rId3"/>
+    <sheet name="Reward Type 2" sheetId="4" r:id="rId4"/>
+    <sheet name="Rate change" sheetId="2" r:id="rId5"/>
+    <sheet name="Boundary " sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="33">
   <si>
     <t xml:space="preserve">max </t>
   </si>
@@ -130,6 +131,15 @@
   </si>
   <si>
     <t>state - with band 1</t>
+  </si>
+  <si>
+    <t>Need to be kept constant</t>
+  </si>
+  <si>
+    <t>state - with band 2</t>
+  </si>
+  <si>
+    <t>state - with band 3</t>
   </si>
 </sst>
 </file>
@@ -1189,23 +1199,265 @@
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
+          <c:idx val="1"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Reward Type 3'!$F$8</c:f>
+              <c:f>'Reward Type 3'!$C$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Reward Type 3 - band 1</c:v>
+                  <c:v>Reward Type 3 - band_3</c:v>
                 </c:pt>
               </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:ln w="22225" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Reward Type 3'!$A$9:$A$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Reward Type 3'!$C$9:$C$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>-5.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4.4444444444444455</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.6944444444444438</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-2.3611111111111107</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1.7777777777777781</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-1.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.77777777777777768</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.36111111111111138</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.30555555555555547</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.55555555555555558</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.88888888888888884</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.97222222222222221</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.97222222222222221</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.88888888888888884</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.55555555555555558</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.30555555555555547</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.36111111111111138</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-0.77777777777777768</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-1.25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-1.7777777777777781</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-2.3611111111111107</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-3.6944444444444438</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-4.4444444444444455</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-5.25</c:v>
+                </c:pt>
+              </c:numCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4CBE-4BC5-9AE0-5E3686E7F472}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Reward Type 3'!$E$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Reward Type 3 - band 2</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1220,7 +1472,7 @@
               </a:solidFill>
               <a:ln w="15875">
                 <a:solidFill>
-                  <a:schemeClr val="accent4"/>
+                  <a:schemeClr val="accent3"/>
                 </a:solidFill>
                 <a:round/>
               </a:ln>
@@ -1327,11 +1579,251 @@
                   <c:v>30</c:v>
                 </c:pt>
               </c:numCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Reward Type 3'!$F$9:$F$39</c:f>
+              <c:f>'Reward Type 3'!$E$9:$E$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>-13.0625</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-11.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-9.5625</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-6.5625</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-5.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4.0625</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-2.0625</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1.25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.5625</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.4375</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.9375</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.9375</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.4375</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-0.5625</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-1.25</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-2.0625</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-4.0625</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-5.25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-6.5625</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-8</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-9.5625</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-11.25</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-13.0625</c:v>
+                </c:pt>
+              </c:numCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4CBE-4BC5-9AE0-5E3686E7F472}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Reward Type 3'!$G$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Reward Type 3 - band 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Reward Type 3'!$A$9:$A$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Reward Type 3'!$G$9:$G$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
@@ -1454,21 +1946,21 @@
           <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
             <c15:filteredLineSeries>
               <c15:ser>
-                <c:idx val="1"/>
-                <c:order val="1"/>
+                <c:idx val="4"/>
+                <c:order val="4"/>
                 <c:tx>
                   <c:strRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Reward Type 3'!$C$8</c15:sqref>
+                          <c15:sqref>'Reward Type 3'!$J$8</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>Reward Type 3 - band_3</c:v>
+                        <c:v>Reward Type 1</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -1476,7 +1968,7 @@
                 <c:spPr>
                   <a:ln w="22225" cap="rnd">
                     <a:solidFill>
-                      <a:schemeClr val="accent2"/>
+                      <a:schemeClr val="accent5"/>
                     </a:solidFill>
                     <a:round/>
                   </a:ln>
@@ -1598,534 +2090,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Reward Type 3'!$C$9:$C$39</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="31"/>
-                      <c:pt idx="0">
-                        <c:v>-5.25</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>-4.4444444444444455</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>-3.6944444444444438</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>-3</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>-2.3611111111111107</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>-1.7777777777777781</c:v>
-                      </c:pt>
-                      <c:pt idx="6">
-                        <c:v>-1.25</c:v>
-                      </c:pt>
-                      <c:pt idx="7">
-                        <c:v>-0.77777777777777768</c:v>
-                      </c:pt>
-                      <c:pt idx="8">
-                        <c:v>-0.36111111111111138</c:v>
-                      </c:pt>
-                      <c:pt idx="9">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="10">
-                        <c:v>0.30555555555555547</c:v>
-                      </c:pt>
-                      <c:pt idx="11">
-                        <c:v>0.55555555555555558</c:v>
-                      </c:pt>
-                      <c:pt idx="12">
-                        <c:v>0.75</c:v>
-                      </c:pt>
-                      <c:pt idx="13">
-                        <c:v>0.88888888888888884</c:v>
-                      </c:pt>
-                      <c:pt idx="14">
-                        <c:v>0.97222222222222221</c:v>
-                      </c:pt>
-                      <c:pt idx="15">
-                        <c:v>1</c:v>
-                      </c:pt>
-                      <c:pt idx="16">
-                        <c:v>0.97222222222222221</c:v>
-                      </c:pt>
-                      <c:pt idx="17">
-                        <c:v>0.88888888888888884</c:v>
-                      </c:pt>
-                      <c:pt idx="18">
-                        <c:v>0.75</c:v>
-                      </c:pt>
-                      <c:pt idx="19">
-                        <c:v>0.55555555555555558</c:v>
-                      </c:pt>
-                      <c:pt idx="20">
-                        <c:v>0.30555555555555547</c:v>
-                      </c:pt>
-                      <c:pt idx="21">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="22">
-                        <c:v>-0.36111111111111138</c:v>
-                      </c:pt>
-                      <c:pt idx="23">
-                        <c:v>-0.77777777777777768</c:v>
-                      </c:pt>
-                      <c:pt idx="24">
-                        <c:v>-1.25</c:v>
-                      </c:pt>
-                      <c:pt idx="25">
-                        <c:v>-1.7777777777777781</c:v>
-                      </c:pt>
-                      <c:pt idx="26">
-                        <c:v>-2.3611111111111107</c:v>
-                      </c:pt>
-                      <c:pt idx="27">
-                        <c:v>-3</c:v>
-                      </c:pt>
-                      <c:pt idx="28">
-                        <c:v>-3.6944444444444438</c:v>
-                      </c:pt>
-                      <c:pt idx="29">
-                        <c:v>-4.4444444444444455</c:v>
-                      </c:pt>
-                      <c:pt idx="30">
-                        <c:v>-5.25</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:val>
-                <c:smooth val="0"/>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000001-4CBE-4BC5-9AE0-5E3686E7F472}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredLineSeries>
-            <c15:filteredLineSeries>
-              <c15:ser>
-                <c:idx val="2"/>
-                <c:order val="2"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Reward Type 3'!$D$8</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>Reward Type 3 - band 2</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:ln w="22225" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent3"/>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="circle"/>
-                  <c:size val="6"/>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="lt1"/>
-                    </a:solidFill>
-                    <a:ln w="15875">
-                      <a:solidFill>
-                        <a:schemeClr val="accent3"/>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c:marker>
-                <c:cat>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Reward Type 3'!$A$9:$A$39</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="31"/>
-                      <c:pt idx="0">
-                        <c:v>15</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>15.5</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>16</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>16.5</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>17</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>17.5</c:v>
-                      </c:pt>
-                      <c:pt idx="6">
-                        <c:v>18</c:v>
-                      </c:pt>
-                      <c:pt idx="7">
-                        <c:v>18.5</c:v>
-                      </c:pt>
-                      <c:pt idx="8">
-                        <c:v>19</c:v>
-                      </c:pt>
-                      <c:pt idx="9">
-                        <c:v>19.5</c:v>
-                      </c:pt>
-                      <c:pt idx="10">
-                        <c:v>20</c:v>
-                      </c:pt>
-                      <c:pt idx="11">
-                        <c:v>20.5</c:v>
-                      </c:pt>
-                      <c:pt idx="12">
-                        <c:v>21</c:v>
-                      </c:pt>
-                      <c:pt idx="13">
-                        <c:v>21.5</c:v>
-                      </c:pt>
-                      <c:pt idx="14">
-                        <c:v>22</c:v>
-                      </c:pt>
-                      <c:pt idx="15">
-                        <c:v>22.5</c:v>
-                      </c:pt>
-                      <c:pt idx="16">
-                        <c:v>23</c:v>
-                      </c:pt>
-                      <c:pt idx="17">
-                        <c:v>23.5</c:v>
-                      </c:pt>
-                      <c:pt idx="18">
-                        <c:v>24</c:v>
-                      </c:pt>
-                      <c:pt idx="19">
-                        <c:v>24.5</c:v>
-                      </c:pt>
-                      <c:pt idx="20">
-                        <c:v>25</c:v>
-                      </c:pt>
-                      <c:pt idx="21">
-                        <c:v>25.5</c:v>
-                      </c:pt>
-                      <c:pt idx="22">
-                        <c:v>26</c:v>
-                      </c:pt>
-                      <c:pt idx="23">
-                        <c:v>26.5</c:v>
-                      </c:pt>
-                      <c:pt idx="24">
-                        <c:v>27</c:v>
-                      </c:pt>
-                      <c:pt idx="25">
-                        <c:v>27.5</c:v>
-                      </c:pt>
-                      <c:pt idx="26">
-                        <c:v>28</c:v>
-                      </c:pt>
-                      <c:pt idx="27">
-                        <c:v>28.5</c:v>
-                      </c:pt>
-                      <c:pt idx="28">
-                        <c:v>29</c:v>
-                      </c:pt>
-                      <c:pt idx="29">
-                        <c:v>29.5</c:v>
-                      </c:pt>
-                      <c:pt idx="30">
-                        <c:v>30</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:cat>
-                <c:val>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Reward Type 3'!$D$9:$D$39</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="31"/>
-                      <c:pt idx="0">
-                        <c:v>-13.0625</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>-11.25</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>-9.5625</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>-8</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>-6.5625</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>-5.25</c:v>
-                      </c:pt>
-                      <c:pt idx="6">
-                        <c:v>-4.0625</c:v>
-                      </c:pt>
-                      <c:pt idx="7">
-                        <c:v>-3</c:v>
-                      </c:pt>
-                      <c:pt idx="8">
-                        <c:v>-2.0625</c:v>
-                      </c:pt>
-                      <c:pt idx="9">
-                        <c:v>-1.25</c:v>
-                      </c:pt>
-                      <c:pt idx="10">
-                        <c:v>-0.5625</c:v>
-                      </c:pt>
-                      <c:pt idx="11">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="12">
-                        <c:v>0.4375</c:v>
-                      </c:pt>
-                      <c:pt idx="13">
-                        <c:v>0.75</c:v>
-                      </c:pt>
-                      <c:pt idx="14">
-                        <c:v>0.9375</c:v>
-                      </c:pt>
-                      <c:pt idx="15">
-                        <c:v>1</c:v>
-                      </c:pt>
-                      <c:pt idx="16">
-                        <c:v>0.9375</c:v>
-                      </c:pt>
-                      <c:pt idx="17">
-                        <c:v>0.75</c:v>
-                      </c:pt>
-                      <c:pt idx="18">
-                        <c:v>0.4375</c:v>
-                      </c:pt>
-                      <c:pt idx="19">
-                        <c:v>0</c:v>
-                      </c:pt>
-                      <c:pt idx="20">
-                        <c:v>-0.5625</c:v>
-                      </c:pt>
-                      <c:pt idx="21">
-                        <c:v>-1.25</c:v>
-                      </c:pt>
-                      <c:pt idx="22">
-                        <c:v>-2.0625</c:v>
-                      </c:pt>
-                      <c:pt idx="23">
-                        <c:v>-3</c:v>
-                      </c:pt>
-                      <c:pt idx="24">
-                        <c:v>-4.0625</c:v>
-                      </c:pt>
-                      <c:pt idx="25">
-                        <c:v>-5.25</c:v>
-                      </c:pt>
-                      <c:pt idx="26">
-                        <c:v>-6.5625</c:v>
-                      </c:pt>
-                      <c:pt idx="27">
-                        <c:v>-8</c:v>
-                      </c:pt>
-                      <c:pt idx="28">
-                        <c:v>-9.5625</c:v>
-                      </c:pt>
-                      <c:pt idx="29">
-                        <c:v>-11.25</c:v>
-                      </c:pt>
-                      <c:pt idx="30">
-                        <c:v>-13.0625</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:val>
-                <c:smooth val="0"/>
-                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000002-4CBE-4BC5-9AE0-5E3686E7F472}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredLineSeries>
-            <c15:filteredLineSeries>
-              <c15:ser>
-                <c:idx val="4"/>
-                <c:order val="4"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Reward Type 3'!$I$8</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>Reward Type 1</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:ln w="22225" cap="rnd">
-                    <a:solidFill>
-                      <a:schemeClr val="accent5"/>
-                    </a:solidFill>
-                    <a:round/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="none"/>
-                </c:marker>
-                <c:cat>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Reward Type 3'!$A$9:$A$39</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="31"/>
-                      <c:pt idx="0">
-                        <c:v>15</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>15.5</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>16</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>16.5</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>17</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>17.5</c:v>
-                      </c:pt>
-                      <c:pt idx="6">
-                        <c:v>18</c:v>
-                      </c:pt>
-                      <c:pt idx="7">
-                        <c:v>18.5</c:v>
-                      </c:pt>
-                      <c:pt idx="8">
-                        <c:v>19</c:v>
-                      </c:pt>
-                      <c:pt idx="9">
-                        <c:v>19.5</c:v>
-                      </c:pt>
-                      <c:pt idx="10">
-                        <c:v>20</c:v>
-                      </c:pt>
-                      <c:pt idx="11">
-                        <c:v>20.5</c:v>
-                      </c:pt>
-                      <c:pt idx="12">
-                        <c:v>21</c:v>
-                      </c:pt>
-                      <c:pt idx="13">
-                        <c:v>21.5</c:v>
-                      </c:pt>
-                      <c:pt idx="14">
-                        <c:v>22</c:v>
-                      </c:pt>
-                      <c:pt idx="15">
-                        <c:v>22.5</c:v>
-                      </c:pt>
-                      <c:pt idx="16">
-                        <c:v>23</c:v>
-                      </c:pt>
-                      <c:pt idx="17">
-                        <c:v>23.5</c:v>
-                      </c:pt>
-                      <c:pt idx="18">
-                        <c:v>24</c:v>
-                      </c:pt>
-                      <c:pt idx="19">
-                        <c:v>24.5</c:v>
-                      </c:pt>
-                      <c:pt idx="20">
-                        <c:v>25</c:v>
-                      </c:pt>
-                      <c:pt idx="21">
-                        <c:v>25.5</c:v>
-                      </c:pt>
-                      <c:pt idx="22">
-                        <c:v>26</c:v>
-                      </c:pt>
-                      <c:pt idx="23">
-                        <c:v>26.5</c:v>
-                      </c:pt>
-                      <c:pt idx="24">
-                        <c:v>27</c:v>
-                      </c:pt>
-                      <c:pt idx="25">
-                        <c:v>27.5</c:v>
-                      </c:pt>
-                      <c:pt idx="26">
-                        <c:v>28</c:v>
-                      </c:pt>
-                      <c:pt idx="27">
-                        <c:v>28.5</c:v>
-                      </c:pt>
-                      <c:pt idx="28">
-                        <c:v>29</c:v>
-                      </c:pt>
-                      <c:pt idx="29">
-                        <c:v>29.5</c:v>
-                      </c:pt>
-                      <c:pt idx="30">
-                        <c:v>30</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:cat>
-                <c:val>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>'Reward Type 3'!$I$9:$I$39</c15:sqref>
+                          <c15:sqref>'Reward Type 3'!$J$9:$J$39</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2229,7 +2194,7 @@
                   </c:numRef>
                 </c:val>
                 <c:smooth val="0"/>
-                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000004-4CBE-4BC5-9AE0-5E3686E7F472}"/>
                   </c:ext>
@@ -2245,7 +2210,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Reward Type 3'!$G$8</c15:sqref>
+                          <c15:sqref>'Reward Type 3'!$H$8</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2274,7 +2239,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Reward Type 3'!$G$9:$G$39</c15:sqref>
+                          <c15:sqref>'Reward Type 3'!$H$9:$H$39</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2394,7 +2359,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Reward Type 3'!$H$8</c15:sqref>
+                          <c15:sqref>'Reward Type 3'!$I$8</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2425,7 +2390,7 @@
                     <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>'Reward Type 3'!$H$9:$H$39</c15:sqref>
+                          <c15:sqref>'Reward Type 3'!$I$9:$I$39</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -2547,7 +2512,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Reward Type 3'!$E$8</c:f>
+              <c:f>'Reward Type 3'!$F$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2560,6 +2525,246 @@
             <a:ln w="22225" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Reward Type 3'!$A$9:$A$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Reward Type 3'!$F$9:$F$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>-7.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-6.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-5.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-3.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-2.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4CBE-4BC5-9AE0-5E3686E7F472}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Reward Type 3'!$D$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>state - with band 2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2574,213 +2779,113 @@
               </a:solidFill>
               <a:ln w="15875">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:round/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'Reward Type 3'!$A$9:$A$39</c:f>
+              <c:f>'Reward Type 3'!$D$9:$D$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>15</c:v>
+                  <c:v>-3.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.5</c:v>
+                  <c:v>-3.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16</c:v>
+                  <c:v>-3.25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16.5</c:v>
+                  <c:v>-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>17</c:v>
+                  <c:v>-2.75</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>17.5</c:v>
+                  <c:v>-2.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18</c:v>
+                  <c:v>-2.25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>18.5</c:v>
+                  <c:v>-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19</c:v>
+                  <c:v>-1.75</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>19.5</c:v>
+                  <c:v>-1.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>20</c:v>
+                  <c:v>-1.25</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>20.5</c:v>
+                  <c:v>-1</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>21</c:v>
+                  <c:v>-0.75</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>21.5</c:v>
+                  <c:v>-0.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>22</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>22.5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>23.5</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>24.5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>25.5</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>26</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>26.5</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>27.5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>28</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>28.5</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>29.5</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>30</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Reward Type 3'!$E$9:$E$39</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
-                <c:pt idx="0">
-                  <c:v>-7.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-7</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-6.5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-5.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-4.5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-4</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-3.5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-3</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-2.5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>-1.5</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>-1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>-0.5</c:v>
+                  <c:v>-0.25</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>1.5</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="22">
+                  <c:v>1.75</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="24">
+                  <c:v>2.25</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>2.5</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="26">
+                  <c:v>2.75</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="28">
+                  <c:v>3.25</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>3.5</c:v>
                 </c:pt>
-                <c:pt idx="23">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>4.5</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>5.5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>6.5</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>7</c:v>
-                </c:pt>
                 <c:pt idx="30">
-                  <c:v>7.5</c:v>
+                  <c:v>3.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2788,7 +2893,145 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4CBE-4BC5-9AE0-5E3686E7F472}"/>
+              <c16:uniqueId val="{00000000-ECD1-464E-AFAC-2703271C06E9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Reward Type 3'!$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>state - with band 3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Reward Type 3'!$B$9:$B$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>-2.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-2.3333333333333335</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-2.1666666666666665</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.8333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1.6666666666666667</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-1.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1.3333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-1.1666666666666667</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.83333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.66666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.66666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.83333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.1666666666666667</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.3333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.6666666666666667</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.8333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.1666666666666665</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.3333333333333335</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-ECD1-464E-AFAC-2703271C06E9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2835,10 +3078,7 @@
                 <a:pPr>
                   <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="dk1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -2875,10 +3115,7 @@
               <a:pPr>
                 <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -2913,10 +3150,7 @@
             <a:pPr>
               <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -2963,10 +3197,7 @@
                 <a:pPr>
                   <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="dk1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -2995,10 +3226,7 @@
               <a:pPr>
                 <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3027,10 +3255,7 @@
             <a:pPr>
               <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3060,10 +3285,7 @@
                 <a:pPr>
                   <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="dk1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -3092,10 +3314,7 @@
               <a:pPr>
                 <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:sysClr val="windowText" lastClr="000000"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3124,10 +3343,7 @@
             <a:pPr>
               <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -3185,8 +3401,8 @@
           <c:yMode val="edge"/>
           <c:x val="1.1225338404246849E-2"/>
           <c:y val="0.91142535543763092"/>
-          <c:w val="0.97221598911159957"/>
-          <c:h val="7.6652142702020698E-2"/>
+          <c:w val="0.69237552999132523"/>
+          <c:h val="7.130344550915968E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -3204,10 +3420,7 @@
           <a:pPr>
             <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -3249,7 +3462,11 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr sz="1050"/>
+        <a:defRPr sz="1050">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -5706,16 +5923,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>200024</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>76201</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>523874</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7401,20 +7618,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A2F8A9-6E69-4436-A2D1-6259AB34D1E8}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7422,28 +7640,28 @@
         <f>$B$6+C4</f>
         <v>25.5</v>
       </c>
-      <c r="D1">
-        <f>$B$6+D4</f>
+      <c r="E1">
+        <f>$B$6+E4</f>
         <v>24.5</v>
-      </c>
-      <c r="F1">
-        <f>$B$6+F4</f>
-        <v>23.5</v>
       </c>
       <c r="G1">
         <f>$B$6+G4</f>
+        <v>23.5</v>
+      </c>
+      <c r="H1">
+        <f>$B$6+H4</f>
         <v>23.25</v>
       </c>
-      <c r="H1">
-        <f t="shared" ref="H1" si="0">$B$6+H4</f>
+      <c r="I1">
+        <f t="shared" ref="I1" si="0">$B$6+I4</f>
         <v>23</v>
       </c>
-      <c r="I1">
-        <f>$B$6+I4</f>
+      <c r="J1">
+        <f>$B$6+J4</f>
         <v>22.6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -7451,38 +7669,34 @@
         <f>$B$6-C4</f>
         <v>19.5</v>
       </c>
-      <c r="D2">
-        <f>$B$6-D4</f>
+      <c r="E2">
+        <f>$B$6-E4</f>
         <v>20.5</v>
-      </c>
-      <c r="F2">
-        <f>$B$6-F4</f>
-        <v>21.5</v>
       </c>
       <c r="G2">
         <f>$B$6-G4</f>
+        <v>21.5</v>
+      </c>
+      <c r="H2">
+        <f>$B$6-H4</f>
         <v>21.75</v>
       </c>
-      <c r="H2">
-        <f t="shared" ref="H2" si="1">$B$6-H4</f>
+      <c r="I2">
+        <f t="shared" ref="I2" si="1">$B$6-I4</f>
         <v>22</v>
       </c>
-      <c r="I2">
-        <f>$B$6-I4</f>
+      <c r="J2">
+        <f>$B$6-J4</f>
         <v>22.4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C3">
         <f>AVERAGE(C1:C2)</f>
         <v>22.5</v>
       </c>
-      <c r="D3">
-        <f>AVERAGE(D1:D2)</f>
-        <v>22.5</v>
-      </c>
-      <c r="F3">
-        <f>AVERAGE(F1:F2)</f>
+      <c r="E3">
+        <f>AVERAGE(E1:E2)</f>
         <v>22.5</v>
       </c>
       <c r="G3">
@@ -7490,38 +7704,48 @@
         <v>22.5</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3" si="2">AVERAGE(H1:H2)</f>
+        <f>AVERAGE(H1:H2)</f>
         <v>22.5</v>
       </c>
       <c r="I3">
-        <f>AVERAGE(I1:I2)</f>
+        <f t="shared" ref="I3" si="2">AVERAGE(I1:I2)</f>
         <v>22.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="J3">
+        <f>AVERAGE(J1:J2)</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1">
         <v>2</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1"/>
+      <c r="G4" s="1">
         <v>1</v>
       </c>
-      <c r="G4">
+      <c r="H4" s="1">
         <v>0.75</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>0.5</v>
       </c>
-      <c r="I4">
+      <c r="J4" s="1">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -7529,7 +7753,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -7537,1180 +7761,1815 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
         <v>25</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>29</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>26</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>27</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>28</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L8">
+        <v>21.5</v>
+      </c>
+      <c r="M8">
+        <v>22.5</v>
+      </c>
+      <c r="N8">
+        <v>23.5</v>
+      </c>
+      <c r="O8">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>15</v>
       </c>
       <c r="B9">
-        <f>(A9-AVERAGE(C$1:C$2))/(C$1-C$2)</f>
-        <v>-1.25</v>
+        <f>(A9-AVERAGE(C$1:C$2))/$C$4</f>
+        <v>-2.5</v>
       </c>
       <c r="C9">
-        <f t="shared" ref="C9:H18" si="3">1-(($A9-$B$6)/C$4)^2</f>
+        <f t="shared" ref="C9:I18" si="3">1-(($A9-$B$6)/C$4)^2</f>
         <v>-5.25</v>
       </c>
       <c r="D9">
-        <f t="shared" si="3"/>
+        <f>($A9-$E$3)/($E$4)</f>
+        <v>-3.75</v>
+      </c>
+      <c r="E9">
+        <f>1-(($A9-$E$3)/E$4)^2</f>
         <v>-13.0625</v>
       </c>
-      <c r="E9">
-        <f>($A9-$F$3)/($F$4)</f>
+      <c r="F9">
+        <f>($A9-$G$3)/($G$4)</f>
         <v>-7.5</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <f t="shared" si="3"/>
         <v>-55.25</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <f t="shared" si="3"/>
         <v>-99</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <f t="shared" si="3"/>
         <v>-224</v>
       </c>
-      <c r="I9">
-        <f t="shared" ref="I9:I39" si="4">1-(A9-$B$6)^2/(C$1-C$2)</f>
+      <c r="J9">
+        <f t="shared" ref="J9:J39" si="4">1-(A9-$B$6)^2/(C$1-C$2)</f>
         <v>-8.375</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L9">
+        <f t="shared" ref="L9:O39" si="5">($A9-L$8)/L$8</f>
+        <v>-0.30232558139534882</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="5"/>
+        <v>-0.33333333333333331</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="5"/>
+        <v>-0.36170212765957449</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="5"/>
+        <v>-0.38775510204081631</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>15.5</v>
       </c>
       <c r="B10">
-        <f t="shared" ref="B10:B39" si="5">(A10-AVERAGE(C$1:C$2))/(C$1-C$2)</f>
-        <v>-1.1666666666666667</v>
+        <f t="shared" ref="B10:B39" si="6">(A10-AVERAGE(C$1:C$2))/$C$4</f>
+        <v>-2.3333333333333335</v>
       </c>
       <c r="C10">
         <f t="shared" si="3"/>
         <v>-4.4444444444444455</v>
       </c>
       <c r="D10">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D10:D39" si="7">($A10-$E$3)/($E$4)</f>
+        <v>-3.5</v>
+      </c>
+      <c r="E10">
+        <f t="shared" ref="E10:E39" si="8">1-(($A10-$E$3)/E$4)^2</f>
         <v>-11.25</v>
       </c>
-      <c r="E10">
-        <f t="shared" ref="E10:E39" si="6">($A10-$F$3)/($F$4)</f>
+      <c r="F10">
+        <f t="shared" ref="F10:F39" si="9">($A10-$G$3)/($G$4)</f>
         <v>-7</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <f t="shared" si="3"/>
         <v>-48</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <f t="shared" si="3"/>
         <v>-86.111111111111128</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <f t="shared" si="3"/>
         <v>-195</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <f t="shared" si="4"/>
         <v>-7.1666666666666661</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L10">
+        <f t="shared" si="5"/>
+        <v>-0.27906976744186046</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="5"/>
+        <v>-0.31111111111111112</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="5"/>
+        <v>-0.34042553191489361</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="5"/>
+        <v>-0.36734693877551022</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>16</v>
       </c>
       <c r="B11">
-        <f t="shared" si="5"/>
-        <v>-1.0833333333333333</v>
+        <f t="shared" si="6"/>
+        <v>-2.1666666666666665</v>
       </c>
       <c r="C11">
         <f t="shared" si="3"/>
         <v>-3.6944444444444438</v>
       </c>
       <c r="D11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
+        <v>-3.25</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="8"/>
         <v>-9.5625</v>
       </c>
-      <c r="E11">
-        <f t="shared" si="6"/>
+      <c r="F11">
+        <f t="shared" si="9"/>
         <v>-6.5</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <f t="shared" si="3"/>
         <v>-41.25</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <f t="shared" si="3"/>
         <v>-74.1111111111111</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <f t="shared" si="3"/>
         <v>-168</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <f t="shared" si="4"/>
         <v>-6.041666666666667</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L11">
+        <f t="shared" si="5"/>
+        <v>-0.2558139534883721</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="5"/>
+        <v>-0.28888888888888886</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="5"/>
+        <v>-0.31914893617021278</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="5"/>
+        <v>-0.34693877551020408</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>16.5</v>
       </c>
       <c r="B12">
-        <f t="shared" si="5"/>
-        <v>-1</v>
+        <f t="shared" si="6"/>
+        <v>-2</v>
       </c>
       <c r="C12">
         <f t="shared" si="3"/>
         <v>-3</v>
       </c>
       <c r="D12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
+        <v>-3</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="8"/>
         <v>-8</v>
       </c>
-      <c r="E12">
-        <f t="shared" si="6"/>
+      <c r="F12">
+        <f t="shared" si="9"/>
         <v>-6</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <f t="shared" si="3"/>
         <v>-35</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <f t="shared" si="3"/>
         <v>-63</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <f t="shared" si="3"/>
         <v>-143</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <f t="shared" si="4"/>
         <v>-5</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L12">
+        <f t="shared" si="5"/>
+        <v>-0.23255813953488372</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="5"/>
+        <v>-0.26666666666666666</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="5"/>
+        <v>-0.2978723404255319</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="5"/>
+        <v>-0.32653061224489793</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>17</v>
       </c>
       <c r="B13">
-        <f t="shared" si="5"/>
-        <v>-0.91666666666666663</v>
+        <f t="shared" si="6"/>
+        <v>-1.8333333333333333</v>
       </c>
       <c r="C13">
         <f t="shared" si="3"/>
         <v>-2.3611111111111107</v>
       </c>
       <c r="D13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
+        <v>-2.75</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="8"/>
         <v>-6.5625</v>
       </c>
-      <c r="E13">
-        <f t="shared" si="6"/>
+      <c r="F13">
+        <f t="shared" si="9"/>
         <v>-5.5</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <f t="shared" si="3"/>
         <v>-29.25</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <f t="shared" si="3"/>
         <v>-52.777777777777771</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <f t="shared" si="3"/>
         <v>-120</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <f t="shared" si="4"/>
         <v>-4.041666666666667</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L13">
+        <f t="shared" si="5"/>
+        <v>-0.20930232558139536</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="5"/>
+        <v>-0.24444444444444444</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="5"/>
+        <v>-0.27659574468085107</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="5"/>
+        <v>-0.30612244897959184</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>17.5</v>
       </c>
       <c r="B14">
-        <f t="shared" si="5"/>
-        <v>-0.83333333333333337</v>
+        <f t="shared" si="6"/>
+        <v>-1.6666666666666667</v>
       </c>
       <c r="C14">
         <f t="shared" si="3"/>
         <v>-1.7777777777777781</v>
       </c>
       <c r="D14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
+        <v>-2.5</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="8"/>
         <v>-5.25</v>
       </c>
-      <c r="E14">
-        <f t="shared" si="6"/>
+      <c r="F14">
+        <f t="shared" si="9"/>
         <v>-5</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <f t="shared" si="3"/>
         <v>-24</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <f t="shared" si="3"/>
         <v>-43.44444444444445</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <f t="shared" si="3"/>
         <v>-99</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <f t="shared" si="4"/>
         <v>-3.166666666666667</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L14">
+        <f t="shared" si="5"/>
+        <v>-0.18604651162790697</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="5"/>
+        <v>-0.22222222222222221</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="5"/>
+        <v>-0.25531914893617019</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="5"/>
+        <v>-0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>18</v>
       </c>
       <c r="B15">
-        <f t="shared" si="5"/>
-        <v>-0.75</v>
+        <f t="shared" si="6"/>
+        <v>-1.5</v>
       </c>
       <c r="C15">
         <f t="shared" si="3"/>
         <v>-1.25</v>
       </c>
       <c r="D15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
+        <v>-2.25</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="8"/>
         <v>-4.0625</v>
       </c>
-      <c r="E15">
-        <f t="shared" si="6"/>
+      <c r="F15">
+        <f t="shared" si="9"/>
         <v>-4.5</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <f t="shared" si="3"/>
         <v>-19.25</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <f t="shared" si="3"/>
         <v>-35</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <f t="shared" si="3"/>
         <v>-80</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <f t="shared" si="4"/>
         <v>-2.375</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L15">
+        <f t="shared" si="5"/>
+        <v>-0.16279069767441862</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="5"/>
+        <v>-0.2</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="5"/>
+        <v>-0.23404255319148937</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="5"/>
+        <v>-0.26530612244897961</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>18.5</v>
       </c>
       <c r="B16">
-        <f t="shared" si="5"/>
-        <v>-0.66666666666666663</v>
+        <f t="shared" si="6"/>
+        <v>-1.3333333333333333</v>
       </c>
       <c r="C16">
         <f t="shared" si="3"/>
         <v>-0.77777777777777768</v>
       </c>
       <c r="D16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
+        <v>-2</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="8"/>
         <v>-3</v>
       </c>
-      <c r="E16">
-        <f t="shared" si="6"/>
+      <c r="F16">
+        <f t="shared" si="9"/>
         <v>-4</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <f t="shared" si="3"/>
         <v>-15</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <f t="shared" si="3"/>
         <v>-27.444444444444443</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <f t="shared" si="3"/>
         <v>-63</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <f t="shared" si="4"/>
         <v>-1.6666666666666665</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L16">
+        <f t="shared" si="5"/>
+        <v>-0.13953488372093023</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="5"/>
+        <v>-0.17777777777777778</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="5"/>
+        <v>-0.21276595744680851</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="5"/>
+        <v>-0.24489795918367346</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>19</v>
       </c>
       <c r="B17">
-        <f t="shared" si="5"/>
-        <v>-0.58333333333333337</v>
+        <f t="shared" si="6"/>
+        <v>-1.1666666666666667</v>
       </c>
       <c r="C17">
         <f t="shared" si="3"/>
         <v>-0.36111111111111138</v>
       </c>
       <c r="D17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
+        <v>-1.75</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="8"/>
         <v>-2.0625</v>
       </c>
-      <c r="E17">
-        <f t="shared" si="6"/>
+      <c r="F17">
+        <f t="shared" si="9"/>
         <v>-3.5</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <f t="shared" si="3"/>
         <v>-11.25</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <f t="shared" si="3"/>
         <v>-20.777777777777782</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <f t="shared" si="3"/>
         <v>-48</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <f t="shared" si="4"/>
         <v>-1.0416666666666665</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L17">
+        <f t="shared" si="5"/>
+        <v>-0.11627906976744186</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="5"/>
+        <v>-0.15555555555555556</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="5"/>
+        <v>-0.19148936170212766</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="5"/>
+        <v>-0.22448979591836735</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>19.5</v>
       </c>
       <c r="B18">
-        <f t="shared" si="5"/>
-        <v>-0.5</v>
+        <f t="shared" si="6"/>
+        <v>-1</v>
       </c>
       <c r="C18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
+        <v>-1.5</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="8"/>
         <v>-1.25</v>
       </c>
-      <c r="E18">
-        <f t="shared" si="6"/>
+      <c r="F18">
+        <f t="shared" si="9"/>
         <v>-3</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <f t="shared" si="3"/>
         <v>-8</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <f t="shared" si="3"/>
         <v>-15</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <f t="shared" si="3"/>
         <v>-35</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <f t="shared" si="4"/>
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L18">
+        <f t="shared" si="5"/>
+        <v>-9.3023255813953487E-2</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="5"/>
+        <v>-0.13333333333333333</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="5"/>
+        <v>-0.1702127659574468</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="5"/>
+        <v>-0.20408163265306123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>20</v>
       </c>
       <c r="B19">
-        <f t="shared" si="5"/>
-        <v>-0.41666666666666669</v>
+        <f t="shared" si="6"/>
+        <v>-0.83333333333333337</v>
       </c>
       <c r="C19">
-        <f t="shared" ref="C19:H28" si="7">1-(($A19-$B$6)/C$4)^2</f>
+        <f t="shared" ref="C19:I28" si="10">1-(($A19-$B$6)/C$4)^2</f>
         <v>0.30555555555555547</v>
       </c>
       <c r="D19">
         <f t="shared" si="7"/>
+        <v>-1.25</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="8"/>
         <v>-0.5625</v>
       </c>
-      <c r="E19">
-        <f t="shared" si="6"/>
+      <c r="F19">
+        <f t="shared" si="9"/>
         <v>-2.5</v>
       </c>
-      <c r="F19">
-        <f t="shared" si="7"/>
+      <c r="G19">
+        <f t="shared" si="10"/>
         <v>-5.25</v>
       </c>
-      <c r="G19">
-        <f t="shared" si="7"/>
+      <c r="H19">
+        <f t="shared" si="10"/>
         <v>-10.111111111111112</v>
       </c>
-      <c r="H19">
-        <f t="shared" si="7"/>
+      <c r="I19">
+        <f t="shared" si="10"/>
         <v>-24</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <f t="shared" si="4"/>
         <v>-4.1666666666666741E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L19">
+        <f t="shared" si="5"/>
+        <v>-6.9767441860465115E-2</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="5"/>
+        <v>-0.1111111111111111</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="5"/>
+        <v>-0.14893617021276595</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="5"/>
+        <v>-0.18367346938775511</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20.5</v>
       </c>
       <c r="B20">
-        <f t="shared" si="5"/>
-        <v>-0.33333333333333331</v>
+        <f t="shared" si="6"/>
+        <v>-0.66666666666666663</v>
       </c>
       <c r="C20">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="D20">
         <f t="shared" si="7"/>
+        <v>-1</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="E20">
-        <f t="shared" si="6"/>
+      <c r="F20">
+        <f t="shared" si="9"/>
         <v>-2</v>
       </c>
-      <c r="F20">
-        <f t="shared" si="7"/>
+      <c r="G20">
+        <f t="shared" si="10"/>
         <v>-3</v>
       </c>
-      <c r="G20">
-        <f t="shared" si="7"/>
+      <c r="H20">
+        <f t="shared" si="10"/>
         <v>-6.1111111111111107</v>
       </c>
-      <c r="H20">
-        <f t="shared" si="7"/>
+      <c r="I20">
+        <f t="shared" si="10"/>
         <v>-15</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <f t="shared" si="4"/>
         <v>0.33333333333333337</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L20">
+        <f t="shared" si="5"/>
+        <v>-4.6511627906976744E-2</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="5"/>
+        <v>-8.8888888888888892E-2</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="5"/>
+        <v>-0.1276595744680851</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="5"/>
+        <v>-0.16326530612244897</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
       <c r="B21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
+        <v>-0.5</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="10"/>
+        <v>0.75</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="7"/>
+        <v>-0.75</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="8"/>
+        <v>0.4375</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="9"/>
+        <v>-1.5</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="10"/>
+        <v>-1.25</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="10"/>
+        <v>-3</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="4"/>
+        <v>0.625</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="5"/>
+        <v>-2.3255813953488372E-2</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="5"/>
+        <v>-6.6666666666666666E-2</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="5"/>
+        <v>-0.10638297872340426</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="5"/>
+        <v>-0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21.5</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="6"/>
+        <v>-0.33333333333333331</v>
+      </c>
+      <c r="C22" s="1">
+        <f t="shared" si="10"/>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="7"/>
+        <v>-0.5</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="8"/>
+        <v>0.75</v>
+      </c>
+      <c r="F22" s="1">
+        <f t="shared" si="9"/>
+        <v>-1</v>
+      </c>
+      <c r="G22" s="1">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="10"/>
+        <v>-0.77777777777777768</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="10"/>
+        <v>-3</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="4"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="5"/>
+        <v>-4.4444444444444446E-2</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="5"/>
+        <v>-8.5106382978723402E-2</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="5"/>
+        <v>-0.12244897959183673</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="6"/>
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="C23" s="1">
+        <f t="shared" si="10"/>
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="7"/>
         <v>-0.25</v>
       </c>
-      <c r="C21">
+      <c r="E23">
+        <f t="shared" si="8"/>
+        <v>0.9375</v>
+      </c>
+      <c r="F23" s="1">
+        <f t="shared" si="9"/>
+        <v>-0.5</v>
+      </c>
+      <c r="G23" s="1">
+        <f t="shared" si="10"/>
+        <v>0.75</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="10"/>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="4"/>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="5"/>
+        <v>2.3255813953488372E-2</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="5"/>
+        <v>-2.2222222222222223E-2</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="5"/>
+        <v>-6.3829787234042548E-2</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="5"/>
+        <v>-0.10204081632653061</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="C24" s="1">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="5"/>
+        <v>4.6511627906976744E-2</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="5"/>
+        <v>-4.2553191489361701E-2</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="5"/>
+        <v>-8.1632653061224483E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="6"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="10"/>
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="7"/>
+        <v>0.25</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="8"/>
+        <v>0.9375</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="9"/>
+        <v>0.5</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="10"/>
+        <v>0.75</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="10"/>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="4"/>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="5"/>
+        <v>6.9767441860465115E-2</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="5"/>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="5"/>
+        <v>-2.1276595744680851E-2</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="5"/>
+        <v>-6.1224489795918366E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>23.5</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="6"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="10"/>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="7"/>
+        <v>0.5</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="8"/>
+        <v>0.75</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="10"/>
+        <v>-0.77777777777777768</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="10"/>
+        <v>-3</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="4"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="5"/>
+        <v>9.3023255813953487E-2</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="5"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="5"/>
+        <v>-4.0816326530612242E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="10"/>
+        <v>0.75</v>
+      </c>
+      <c r="D27">
         <f t="shared" si="7"/>
         <v>0.75</v>
       </c>
-      <c r="D21">
-        <f t="shared" si="7"/>
+      <c r="E27">
+        <f t="shared" si="8"/>
         <v>0.4375</v>
       </c>
-      <c r="E21">
+      <c r="F27">
+        <f t="shared" si="9"/>
+        <v>1.5</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="10"/>
+        <v>-1.25</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="10"/>
+        <v>-3</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="4"/>
+        <v>0.625</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="5"/>
+        <v>0.11627906976744186</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="5"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="5"/>
+        <v>2.1276595744680851E-2</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="5"/>
+        <v>-2.0408163265306121E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>24.5</v>
+      </c>
+      <c r="B28">
         <f t="shared" si="6"/>
-        <v>-1.5</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="7"/>
-        <v>-1.25</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="7"/>
-        <v>-3</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="7"/>
-        <v>-8</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="4"/>
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>21.5</v>
-      </c>
-      <c r="B22" s="1">
-        <f t="shared" si="5"/>
-        <v>-0.16666666666666666</v>
-      </c>
-      <c r="C22" s="1">
-        <f t="shared" si="7"/>
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="D22" s="1">
-        <f t="shared" si="7"/>
-        <v>0.75</v>
-      </c>
-      <c r="E22" s="1">
-        <f t="shared" si="6"/>
-        <v>-1</v>
-      </c>
-      <c r="F22" s="1">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="7"/>
-        <v>-0.77777777777777768</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="7"/>
-        <v>-3</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="4"/>
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1">
-        <f t="shared" si="5"/>
-        <v>-8.3333333333333329E-2</v>
-      </c>
-      <c r="C23" s="1">
-        <f t="shared" si="7"/>
-        <v>0.97222222222222221</v>
-      </c>
-      <c r="D23" s="1">
-        <f t="shared" si="7"/>
-        <v>0.9375</v>
-      </c>
-      <c r="E23" s="1">
-        <f t="shared" si="6"/>
-        <v>-0.5</v>
-      </c>
-      <c r="F23" s="1">
-        <f t="shared" si="7"/>
-        <v>0.75</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="7"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="10"/>
         <v>0.55555555555555558</v>
       </c>
-      <c r="H23">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <f t="shared" si="4"/>
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>22.5</v>
-      </c>
-      <c r="B24" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="C24" s="1">
+      <c r="D28">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="D24" s="1">
+      <c r="E28">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="10"/>
+        <v>-3</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="10"/>
+        <v>-6.1111111111111107</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="10"/>
+        <v>-15</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333337</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="5"/>
+        <v>0.13953488372093023</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="5"/>
+        <v>8.8888888888888892E-2</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="5"/>
+        <v>4.2553191489361701E-2</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>25</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="6"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C29">
+        <f t="shared" ref="C29:I39" si="11">1-(($A29-$B$6)/C$4)^2</f>
+        <v>0.30555555555555547</v>
+      </c>
+      <c r="D29">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="E24" s="1">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F24" s="1">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25">
-        <f t="shared" si="5"/>
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="C25">
-        <f t="shared" si="7"/>
-        <v>0.97222222222222221</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="7"/>
-        <v>0.9375</v>
-      </c>
-      <c r="E25">
-        <f t="shared" si="6"/>
-        <v>0.5</v>
-      </c>
-      <c r="F25">
-        <f t="shared" si="7"/>
-        <v>0.75</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="7"/>
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="H25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <f t="shared" si="4"/>
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>23.5</v>
-      </c>
-      <c r="B26">
-        <f t="shared" si="5"/>
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="C26">
-        <f t="shared" si="7"/>
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="7"/>
-        <v>0.75</v>
-      </c>
-      <c r="E26">
+        <v>1.25</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="8"/>
+        <v>-0.5625</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="9"/>
+        <v>2.5</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="11"/>
+        <v>-5.25</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="11"/>
+        <v>-10.111111111111112</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="11"/>
+        <v>-24</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="4"/>
+        <v>-4.1666666666666741E-2</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="5"/>
+        <v>0.16279069767441862</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="5"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="5"/>
+        <v>6.3829787234042548E-2</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="5"/>
+        <v>2.0408163265306121E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>25.5</v>
+      </c>
+      <c r="B30">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="F26">
+      <c r="C30">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="D30">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G26">
+        <v>1.5</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="8"/>
+        <v>-1.25</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="11"/>
+        <v>-8</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="11"/>
+        <v>-15</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="11"/>
+        <v>-35</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="4"/>
+        <v>-0.5</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="5"/>
+        <v>0.18604651162790697</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="5"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="5"/>
+        <v>8.5106382978723402E-2</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="5"/>
+        <v>4.0816326530612242E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>26</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="6"/>
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="11"/>
+        <v>-0.36111111111111138</v>
+      </c>
+      <c r="D31">
         <f t="shared" si="7"/>
+        <v>1.75</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="8"/>
+        <v>-2.0625</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="9"/>
+        <v>3.5</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="11"/>
+        <v>-11.25</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="11"/>
+        <v>-20.777777777777782</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="11"/>
+        <v>-48</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="4"/>
+        <v>-1.0416666666666665</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="5"/>
+        <v>0.20930232558139536</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="5"/>
+        <v>0.15555555555555556</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="5"/>
+        <v>0.10638297872340426</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="5"/>
+        <v>6.1224489795918366E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>26.5</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="6"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="11"/>
         <v>-0.77777777777777768</v>
       </c>
-      <c r="H26">
+      <c r="D32">
         <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="8"/>
         <v>-3</v>
       </c>
-      <c r="I26">
-        <f t="shared" si="4"/>
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>24</v>
-      </c>
-      <c r="B27">
-        <f t="shared" si="5"/>
-        <v>0.25</v>
-      </c>
-      <c r="C27">
-        <f t="shared" si="7"/>
-        <v>0.75</v>
-      </c>
-      <c r="D27">
-        <f t="shared" si="7"/>
-        <v>0.4375</v>
-      </c>
-      <c r="E27">
+      <c r="F32">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="11"/>
+        <v>-15</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="11"/>
+        <v>-27.444444444444443</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="11"/>
+        <v>-63</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="4"/>
+        <v>-1.6666666666666665</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="5"/>
+        <v>0.23255813953488372</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="5"/>
+        <v>0.17777777777777778</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="5"/>
+        <v>0.1276595744680851</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="5"/>
+        <v>8.1632653061224483E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>27</v>
+      </c>
+      <c r="B33">
         <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
-      <c r="F27">
+      <c r="C33">
+        <f t="shared" si="11"/>
+        <v>-1.25</v>
+      </c>
+      <c r="D33">
         <f t="shared" si="7"/>
-        <v>-1.25</v>
-      </c>
-      <c r="G27">
+        <v>2.25</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="8"/>
+        <v>-4.0625</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="9"/>
+        <v>4.5</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="11"/>
+        <v>-19.25</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="11"/>
+        <v>-35</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="11"/>
+        <v>-80</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="4"/>
+        <v>-2.375</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="5"/>
+        <v>0.2558139534883721</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="5"/>
+        <v>0.2</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="5"/>
+        <v>0.14893617021276595</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="5"/>
+        <v>0.10204081632653061</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>27.5</v>
+      </c>
+      <c r="B34">
+        <f t="shared" si="6"/>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="11"/>
+        <v>-1.7777777777777781</v>
+      </c>
+      <c r="D34">
         <f t="shared" si="7"/>
-        <v>-3</v>
-      </c>
-      <c r="H27">
+        <v>2.5</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="8"/>
+        <v>-5.25</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="11"/>
+        <v>-24</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="11"/>
+        <v>-43.44444444444445</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="11"/>
+        <v>-99</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="4"/>
+        <v>-3.166666666666667</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="5"/>
+        <v>0.27906976744186046</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="5"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="5"/>
+        <v>0.1702127659574468</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="5"/>
+        <v>0.12244897959183673</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>28</v>
+      </c>
+      <c r="B35">
+        <f t="shared" si="6"/>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="11"/>
+        <v>-2.3611111111111107</v>
+      </c>
+      <c r="D35">
         <f t="shared" si="7"/>
-        <v>-8</v>
-      </c>
-      <c r="I27">
-        <f t="shared" si="4"/>
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>24.5</v>
-      </c>
-      <c r="B28">
-        <f t="shared" si="5"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C28">
-        <f t="shared" si="7"/>
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="D28">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="E28">
+        <v>2.75</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="8"/>
+        <v>-6.5625</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="9"/>
+        <v>5.5</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="11"/>
+        <v>-29.25</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="11"/>
+        <v>-52.777777777777771</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="11"/>
+        <v>-120</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="4"/>
+        <v>-4.041666666666667</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="5"/>
+        <v>0.30232558139534882</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="5"/>
+        <v>0.24444444444444444</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="5"/>
+        <v>0.19148936170212766</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="5"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>28.5</v>
+      </c>
+      <c r="B36">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="F28">
+      <c r="C36">
+        <f t="shared" si="11"/>
+        <v>-3</v>
+      </c>
+      <c r="D36">
         <f t="shared" si="7"/>
-        <v>-3</v>
-      </c>
-      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="8"/>
+        <v>-8</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="9"/>
+        <v>6</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="11"/>
+        <v>-35</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="11"/>
+        <v>-63</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="11"/>
+        <v>-143</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="4"/>
+        <v>-5</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="5"/>
+        <v>0.32558139534883723</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="5"/>
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="5"/>
+        <v>0.21276595744680851</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="5"/>
+        <v>0.16326530612244897</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>29</v>
+      </c>
+      <c r="B37">
+        <f t="shared" si="6"/>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="11"/>
+        <v>-3.6944444444444438</v>
+      </c>
+      <c r="D37">
         <f t="shared" si="7"/>
-        <v>-6.1111111111111107</v>
-      </c>
-      <c r="H28">
+        <v>3.25</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="8"/>
+        <v>-9.5625</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="9"/>
+        <v>6.5</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="11"/>
+        <v>-41.25</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="11"/>
+        <v>-74.1111111111111</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="11"/>
+        <v>-168</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="4"/>
+        <v>-6.041666666666667</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="5"/>
+        <v>0.34883720930232559</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="5"/>
+        <v>0.28888888888888886</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="5"/>
+        <v>0.23404255319148937</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="5"/>
+        <v>0.18367346938775511</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>29.5</v>
+      </c>
+      <c r="B38">
+        <f t="shared" si="6"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="11"/>
+        <v>-4.4444444444444455</v>
+      </c>
+      <c r="D38">
         <f t="shared" si="7"/>
-        <v>-15</v>
-      </c>
-      <c r="I28">
-        <f t="shared" si="4"/>
-        <v>0.33333333333333337</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>25</v>
-      </c>
-      <c r="B29">
-        <f t="shared" si="5"/>
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C29">
-        <f t="shared" ref="C29:H39" si="8">1-(($A29-$B$6)/C$4)^2</f>
-        <v>0.30555555555555547</v>
-      </c>
-      <c r="D29">
+        <v>3.5</v>
+      </c>
+      <c r="E38">
         <f t="shared" si="8"/>
-        <v>-0.5625</v>
-      </c>
-      <c r="E29">
+        <v>-11.25</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="11"/>
+        <v>-48</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="11"/>
+        <v>-86.111111111111128</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="11"/>
+        <v>-195</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="4"/>
+        <v>-7.1666666666666661</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="5"/>
+        <v>0.37209302325581395</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="5"/>
+        <v>0.31111111111111112</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="5"/>
+        <v>0.25531914893617019</v>
+      </c>
+      <c r="O38">
+        <f t="shared" si="5"/>
+        <v>0.20408163265306123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>30</v>
+      </c>
+      <c r="B39">
         <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
-      <c r="F29">
-        <f t="shared" si="8"/>
+      <c r="C39">
+        <f t="shared" si="11"/>
         <v>-5.25</v>
       </c>
-      <c r="G29">
-        <f t="shared" si="8"/>
-        <v>-10.111111111111112</v>
-      </c>
-      <c r="H29">
-        <f t="shared" si="8"/>
-        <v>-24</v>
-      </c>
-      <c r="I29">
-        <f t="shared" si="4"/>
-        <v>-4.1666666666666741E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>25.5</v>
-      </c>
-      <c r="B30">
-        <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="C30">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <f t="shared" si="8"/>
-        <v>-1.25</v>
-      </c>
-      <c r="E30">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="F30">
-        <f t="shared" si="8"/>
-        <v>-8</v>
-      </c>
-      <c r="G30">
-        <f t="shared" si="8"/>
-        <v>-15</v>
-      </c>
-      <c r="H30">
-        <f t="shared" si="8"/>
-        <v>-35</v>
-      </c>
-      <c r="I30">
-        <f t="shared" si="4"/>
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>26</v>
-      </c>
-      <c r="B31">
-        <f t="shared" si="5"/>
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="C31">
-        <f t="shared" si="8"/>
-        <v>-0.36111111111111138</v>
-      </c>
-      <c r="D31">
-        <f t="shared" si="8"/>
-        <v>-2.0625</v>
-      </c>
-      <c r="E31">
-        <f t="shared" si="6"/>
-        <v>3.5</v>
-      </c>
-      <c r="F31">
-        <f t="shared" si="8"/>
-        <v>-11.25</v>
-      </c>
-      <c r="G31">
-        <f t="shared" si="8"/>
-        <v>-20.777777777777782</v>
-      </c>
-      <c r="H31">
-        <f t="shared" si="8"/>
-        <v>-48</v>
-      </c>
-      <c r="I31">
-        <f t="shared" si="4"/>
-        <v>-1.0416666666666665</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>26.5</v>
-      </c>
-      <c r="B32">
-        <f t="shared" si="5"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C32">
-        <f t="shared" si="8"/>
-        <v>-0.77777777777777768</v>
-      </c>
-      <c r="D32">
-        <f t="shared" si="8"/>
-        <v>-3</v>
-      </c>
-      <c r="E32">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="F32">
-        <f t="shared" si="8"/>
-        <v>-15</v>
-      </c>
-      <c r="G32">
-        <f t="shared" si="8"/>
-        <v>-27.444444444444443</v>
-      </c>
-      <c r="H32">
-        <f t="shared" si="8"/>
-        <v>-63</v>
-      </c>
-      <c r="I32">
-        <f t="shared" si="4"/>
-        <v>-1.6666666666666665</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>27</v>
-      </c>
-      <c r="B33">
-        <f t="shared" si="5"/>
-        <v>0.75</v>
-      </c>
-      <c r="C33">
-        <f t="shared" si="8"/>
-        <v>-1.25</v>
-      </c>
-      <c r="D33">
-        <f t="shared" si="8"/>
-        <v>-4.0625</v>
-      </c>
-      <c r="E33">
-        <f t="shared" si="6"/>
-        <v>4.5</v>
-      </c>
-      <c r="F33">
-        <f t="shared" si="8"/>
-        <v>-19.25</v>
-      </c>
-      <c r="G33">
-        <f t="shared" si="8"/>
-        <v>-35</v>
-      </c>
-      <c r="H33">
-        <f t="shared" si="8"/>
-        <v>-80</v>
-      </c>
-      <c r="I33">
-        <f t="shared" si="4"/>
-        <v>-2.375</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>27.5</v>
-      </c>
-      <c r="B34">
-        <f t="shared" si="5"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="C34">
-        <f t="shared" si="8"/>
-        <v>-1.7777777777777781</v>
-      </c>
-      <c r="D34">
-        <f t="shared" si="8"/>
-        <v>-5.25</v>
-      </c>
-      <c r="E34">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="F34">
-        <f t="shared" si="8"/>
-        <v>-24</v>
-      </c>
-      <c r="G34">
-        <f t="shared" si="8"/>
-        <v>-43.44444444444445</v>
-      </c>
-      <c r="H34">
-        <f t="shared" si="8"/>
-        <v>-99</v>
-      </c>
-      <c r="I34">
-        <f t="shared" si="4"/>
-        <v>-3.166666666666667</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>28</v>
-      </c>
-      <c r="B35">
-        <f t="shared" si="5"/>
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="C35">
-        <f t="shared" si="8"/>
-        <v>-2.3611111111111107</v>
-      </c>
-      <c r="D35">
-        <f t="shared" si="8"/>
-        <v>-6.5625</v>
-      </c>
-      <c r="E35">
-        <f t="shared" si="6"/>
-        <v>5.5</v>
-      </c>
-      <c r="F35">
-        <f t="shared" si="8"/>
-        <v>-29.25</v>
-      </c>
-      <c r="G35">
-        <f t="shared" si="8"/>
-        <v>-52.777777777777771</v>
-      </c>
-      <c r="H35">
-        <f t="shared" si="8"/>
-        <v>-120</v>
-      </c>
-      <c r="I35">
-        <f t="shared" si="4"/>
-        <v>-4.041666666666667</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>28.5</v>
-      </c>
-      <c r="B36">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="C36">
-        <f t="shared" si="8"/>
-        <v>-3</v>
-      </c>
-      <c r="D36">
-        <f t="shared" si="8"/>
-        <v>-8</v>
-      </c>
-      <c r="E36">
-        <f t="shared" si="6"/>
-        <v>6</v>
-      </c>
-      <c r="F36">
-        <f t="shared" si="8"/>
-        <v>-35</v>
-      </c>
-      <c r="G36">
-        <f t="shared" si="8"/>
-        <v>-63</v>
-      </c>
-      <c r="H36">
-        <f t="shared" si="8"/>
-        <v>-143</v>
-      </c>
-      <c r="I36">
-        <f t="shared" si="4"/>
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>29</v>
-      </c>
-      <c r="B37">
-        <f t="shared" si="5"/>
-        <v>1.0833333333333333</v>
-      </c>
-      <c r="C37">
-        <f t="shared" si="8"/>
-        <v>-3.6944444444444438</v>
-      </c>
-      <c r="D37">
-        <f t="shared" si="8"/>
-        <v>-9.5625</v>
-      </c>
-      <c r="E37">
-        <f t="shared" si="6"/>
-        <v>6.5</v>
-      </c>
-      <c r="F37">
-        <f t="shared" si="8"/>
-        <v>-41.25</v>
-      </c>
-      <c r="G37">
-        <f t="shared" si="8"/>
-        <v>-74.1111111111111</v>
-      </c>
-      <c r="H37">
-        <f t="shared" si="8"/>
-        <v>-168</v>
-      </c>
-      <c r="I37">
-        <f t="shared" si="4"/>
-        <v>-6.041666666666667</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>29.5</v>
-      </c>
-      <c r="B38">
-        <f t="shared" si="5"/>
-        <v>1.1666666666666667</v>
-      </c>
-      <c r="C38">
-        <f t="shared" si="8"/>
-        <v>-4.4444444444444455</v>
-      </c>
-      <c r="D38">
-        <f t="shared" si="8"/>
-        <v>-11.25</v>
-      </c>
-      <c r="E38">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="F38">
-        <f t="shared" si="8"/>
-        <v>-48</v>
-      </c>
-      <c r="G38">
-        <f t="shared" si="8"/>
-        <v>-86.111111111111128</v>
-      </c>
-      <c r="H38">
-        <f t="shared" si="8"/>
-        <v>-195</v>
-      </c>
-      <c r="I38">
-        <f t="shared" si="4"/>
-        <v>-7.1666666666666661</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>30</v>
-      </c>
-      <c r="B39">
-        <f t="shared" si="5"/>
-        <v>1.25</v>
-      </c>
-      <c r="C39">
-        <f t="shared" si="8"/>
-        <v>-5.25</v>
-      </c>
       <c r="D39">
+        <f t="shared" si="7"/>
+        <v>3.75</v>
+      </c>
+      <c r="E39">
         <f t="shared" si="8"/>
         <v>-13.0625</v>
       </c>
-      <c r="E39">
-        <f t="shared" si="6"/>
+      <c r="F39">
+        <f t="shared" si="9"/>
         <v>7.5</v>
       </c>
-      <c r="F39">
-        <f t="shared" si="8"/>
+      <c r="G39">
+        <f t="shared" si="11"/>
         <v>-55.25</v>
       </c>
-      <c r="G39">
-        <f t="shared" si="8"/>
+      <c r="H39">
+        <f t="shared" si="11"/>
         <v>-99</v>
       </c>
-      <c r="H39">
-        <f t="shared" si="8"/>
+      <c r="I39">
+        <f t="shared" si="11"/>
         <v>-224</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <f t="shared" si="4"/>
         <v>-8.375</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="5"/>
+        <v>0.39534883720930231</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="5"/>
+        <v>0.27659574468085107</v>
+      </c>
+      <c r="O39">
+        <f t="shared" si="5"/>
+        <v>0.22448979591836735</v>
       </c>
     </row>
   </sheetData>
@@ -8721,6 +9580,1839 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20B29F27-AD17-46E6-BD5E-59A5C1183A49}">
+  <dimension ref="A1:O39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1">
+        <f>$B$6+C4</f>
+        <v>25.5</v>
+      </c>
+      <c r="E1">
+        <f>$B$6+E4</f>
+        <v>24.5</v>
+      </c>
+      <c r="G1">
+        <f>$B$6+G4</f>
+        <v>23.5</v>
+      </c>
+      <c r="H1">
+        <f>$B$6+H4</f>
+        <v>23.25</v>
+      </c>
+      <c r="I1">
+        <f t="shared" ref="I1" si="0">$B$6+I4</f>
+        <v>23</v>
+      </c>
+      <c r="J1">
+        <f>$B$6+J4</f>
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <f>$B$6-C4</f>
+        <v>19.5</v>
+      </c>
+      <c r="E2">
+        <f>$B$6-E4</f>
+        <v>20.5</v>
+      </c>
+      <c r="G2">
+        <f>$B$6-G4</f>
+        <v>21.5</v>
+      </c>
+      <c r="H2">
+        <f>$B$6-H4</f>
+        <v>21.75</v>
+      </c>
+      <c r="I2">
+        <f t="shared" ref="I2" si="1">$B$6-I4</f>
+        <v>22</v>
+      </c>
+      <c r="J2">
+        <f>$B$6-J4</f>
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C3">
+        <f>AVERAGE(C1:C2)</f>
+        <v>22.5</v>
+      </c>
+      <c r="E3">
+        <f>AVERAGE(E1:E2)</f>
+        <v>22.5</v>
+      </c>
+      <c r="G3">
+        <f>AVERAGE(G1:G2)</f>
+        <v>22.5</v>
+      </c>
+      <c r="H3">
+        <f>AVERAGE(H1:H2)</f>
+        <v>22.5</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3" si="2">AVERAGE(I1:I2)</f>
+        <v>22.5</v>
+      </c>
+      <c r="J3">
+        <f>AVERAGE(J1:J2)</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8">
+        <v>21.5</v>
+      </c>
+      <c r="M8">
+        <v>22.5</v>
+      </c>
+      <c r="N8">
+        <v>23.5</v>
+      </c>
+      <c r="O8">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>15</v>
+      </c>
+      <c r="B9">
+        <f>(A9-AVERAGE(C$1:C$2))/$C$4</f>
+        <v>-2.5</v>
+      </c>
+      <c r="C9">
+        <f>1-(2*($A9-$B$6)/C$4)^2</f>
+        <v>-24</v>
+      </c>
+      <c r="D9">
+        <f>($A9-$E$3)/($E$4)</f>
+        <v>-3.75</v>
+      </c>
+      <c r="E9">
+        <f>1-(($A9-$E$3)/E$4)^2</f>
+        <v>-13.0625</v>
+      </c>
+      <c r="F9">
+        <f>($A9-$G$3)/($G$4)</f>
+        <v>-7.5</v>
+      </c>
+      <c r="G9">
+        <f t="shared" ref="C9:I24" si="3">1-(($A9-$B$6)/G$4)^2</f>
+        <v>-55.25</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="3"/>
+        <v>-99</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="3"/>
+        <v>-224</v>
+      </c>
+      <c r="L9">
+        <f t="shared" ref="L9:O39" si="4">($A9-L$8)/L$8</f>
+        <v>-0.30232558139534882</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="4"/>
+        <v>-0.33333333333333331</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="4"/>
+        <v>-0.36170212765957449</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="4"/>
+        <v>-0.38775510204081631</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>15.5</v>
+      </c>
+      <c r="B10">
+        <f t="shared" ref="B10:B39" si="5">(A10-AVERAGE(C$1:C$2))/$C$4</f>
+        <v>-2.3333333333333335</v>
+      </c>
+      <c r="C10">
+        <f t="shared" ref="C10:C39" si="6">1-(2*($A10-$B$6)/C$4)^2</f>
+        <v>-20.777777777777782</v>
+      </c>
+      <c r="D10">
+        <f t="shared" ref="D10:D39" si="7">($A10-$E$3)/($E$4)</f>
+        <v>-3.5</v>
+      </c>
+      <c r="E10">
+        <f t="shared" ref="E10:E39" si="8">1-(($A10-$E$3)/E$4)^2</f>
+        <v>-11.25</v>
+      </c>
+      <c r="F10">
+        <f t="shared" ref="F10:F39" si="9">($A10-$G$3)/($G$4)</f>
+        <v>-7</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="3"/>
+        <v>-48</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="3"/>
+        <v>-86.111111111111128</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="3"/>
+        <v>-195</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="4"/>
+        <v>-0.27906976744186046</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="4"/>
+        <v>-0.31111111111111112</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="4"/>
+        <v>-0.34042553191489361</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="4"/>
+        <v>-0.36734693877551022</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="5"/>
+        <v>-2.1666666666666665</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="6"/>
+        <v>-17.777777777777775</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="7"/>
+        <v>-3.25</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="8"/>
+        <v>-9.5625</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="9"/>
+        <v>-6.5</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="3"/>
+        <v>-41.25</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="3"/>
+        <v>-74.1111111111111</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="3"/>
+        <v>-168</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="4"/>
+        <v>-0.2558139534883721</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="4"/>
+        <v>-0.28888888888888886</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="4"/>
+        <v>-0.31914893617021278</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="4"/>
+        <v>-0.34693877551020408</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>16.5</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="5"/>
+        <v>-2</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="6"/>
+        <v>-15</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="7"/>
+        <v>-3</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="8"/>
+        <v>-8</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="9"/>
+        <v>-6</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="3"/>
+        <v>-35</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="3"/>
+        <v>-63</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="3"/>
+        <v>-143</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="4"/>
+        <v>-0.23255813953488372</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="4"/>
+        <v>-0.26666666666666666</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="4"/>
+        <v>-0.2978723404255319</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="4"/>
+        <v>-0.32653061224489793</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="5"/>
+        <v>-1.8333333333333333</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="6"/>
+        <v>-12.444444444444443</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="7"/>
+        <v>-2.75</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="8"/>
+        <v>-6.5625</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="9"/>
+        <v>-5.5</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="3"/>
+        <v>-29.25</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="3"/>
+        <v>-52.777777777777771</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="3"/>
+        <v>-120</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="4"/>
+        <v>-0.20930232558139536</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="4"/>
+        <v>-0.24444444444444444</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="4"/>
+        <v>-0.27659574468085107</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="4"/>
+        <v>-0.30612244897959184</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>17.5</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="5"/>
+        <v>-1.6666666666666667</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="6"/>
+        <v>-10.111111111111112</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="7"/>
+        <v>-2.5</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="8"/>
+        <v>-5.25</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="9"/>
+        <v>-5</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="3"/>
+        <v>-24</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="3"/>
+        <v>-43.44444444444445</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="3"/>
+        <v>-99</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="4"/>
+        <v>-0.18604651162790697</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="4"/>
+        <v>-0.22222222222222221</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="4"/>
+        <v>-0.25531914893617019</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="4"/>
+        <v>-0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="5"/>
+        <v>-1.5</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="6"/>
+        <v>-8</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="7"/>
+        <v>-2.25</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="8"/>
+        <v>-4.0625</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="9"/>
+        <v>-4.5</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="3"/>
+        <v>-19.25</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="3"/>
+        <v>-35</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="3"/>
+        <v>-80</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="4"/>
+        <v>-0.16279069767441862</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="4"/>
+        <v>-0.2</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="4"/>
+        <v>-0.23404255319148937</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="4"/>
+        <v>-0.26530612244897961</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>18.5</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="5"/>
+        <v>-1.3333333333333333</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="6"/>
+        <v>-6.1111111111111107</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="7"/>
+        <v>-2</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="8"/>
+        <v>-3</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="9"/>
+        <v>-4</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="3"/>
+        <v>-15</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="3"/>
+        <v>-27.444444444444443</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="3"/>
+        <v>-63</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="4"/>
+        <v>-0.13953488372093023</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="4"/>
+        <v>-0.17777777777777778</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="4"/>
+        <v>-0.21276595744680851</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="4"/>
+        <v>-0.24489795918367346</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="5"/>
+        <v>-1.1666666666666667</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="6"/>
+        <v>-4.4444444444444455</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="7"/>
+        <v>-1.75</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="8"/>
+        <v>-2.0625</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="9"/>
+        <v>-3.5</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="3"/>
+        <v>-11.25</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="3"/>
+        <v>-20.777777777777782</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="3"/>
+        <v>-48</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="4"/>
+        <v>-0.11627906976744186</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="4"/>
+        <v>-0.15555555555555556</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="4"/>
+        <v>-0.19148936170212766</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="4"/>
+        <v>-0.22448979591836735</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>19.5</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="5"/>
+        <v>-1</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="6"/>
+        <v>-3</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="7"/>
+        <v>-1.5</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="8"/>
+        <v>-1.25</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="9"/>
+        <v>-3</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="3"/>
+        <v>-8</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="3"/>
+        <v>-15</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="3"/>
+        <v>-35</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="4"/>
+        <v>-9.3023255813953487E-2</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="4"/>
+        <v>-0.13333333333333333</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="4"/>
+        <v>-0.1702127659574468</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="4"/>
+        <v>-0.20408163265306123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="5"/>
+        <v>-0.83333333333333337</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="6"/>
+        <v>-1.7777777777777781</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="7"/>
+        <v>-1.25</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="8"/>
+        <v>-0.5625</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="9"/>
+        <v>-2.5</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="3"/>
+        <v>-5.25</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="3"/>
+        <v>-10.111111111111112</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="3"/>
+        <v>-24</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="4"/>
+        <v>-6.9767441860465115E-2</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="4"/>
+        <v>-0.1111111111111111</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="4"/>
+        <v>-0.14893617021276595</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="4"/>
+        <v>-0.18367346938775511</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>20.5</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="5"/>
+        <v>-0.66666666666666663</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="6"/>
+        <v>-0.77777777777777768</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="7"/>
+        <v>-1</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="9"/>
+        <v>-2</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="3"/>
+        <v>-3</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="3"/>
+        <v>-6.1111111111111107</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="3"/>
+        <v>-15</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="4"/>
+        <v>-4.6511627906976744E-2</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="4"/>
+        <v>-8.8888888888888892E-2</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="4"/>
+        <v>-0.1276595744680851</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="4"/>
+        <v>-0.16326530612244897</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="5"/>
+        <v>-0.5</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="7"/>
+        <v>-0.75</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="8"/>
+        <v>0.4375</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="9"/>
+        <v>-1.5</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="3"/>
+        <v>-1.25</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="3"/>
+        <v>-3</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="3"/>
+        <v>-8</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="4"/>
+        <v>-2.3255813953488372E-2</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="4"/>
+        <v>-6.6666666666666666E-2</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="4"/>
+        <v>-0.10638297872340426</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="4"/>
+        <v>-0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21.5</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="5"/>
+        <v>-0.33333333333333331</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="6"/>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="7"/>
+        <v>-0.5</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="8"/>
+        <v>0.75</v>
+      </c>
+      <c r="F22" s="1">
+        <f t="shared" si="9"/>
+        <v>-1</v>
+      </c>
+      <c r="G22" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="3"/>
+        <v>-0.77777777777777768</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="3"/>
+        <v>-3</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="4"/>
+        <v>-4.4444444444444446E-2</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="4"/>
+        <v>-8.5106382978723402E-2</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="4"/>
+        <v>-0.12244897959183673</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="5"/>
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="6"/>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="7"/>
+        <v>-0.25</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="8"/>
+        <v>0.9375</v>
+      </c>
+      <c r="F23" s="1">
+        <f t="shared" si="9"/>
+        <v>-0.5</v>
+      </c>
+      <c r="G23" s="1">
+        <f t="shared" si="3"/>
+        <v>0.75</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="3"/>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="4"/>
+        <v>2.3255813953488372E-2</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="4"/>
+        <v>-2.2222222222222223E-2</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="4"/>
+        <v>-6.3829787234042548E-2</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="4"/>
+        <v>-0.10204081632653061</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="4"/>
+        <v>4.6511627906976744E-2</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="4"/>
+        <v>-4.2553191489361701E-2</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="4"/>
+        <v>-8.1632653061224483E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="5"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="6"/>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="7"/>
+        <v>0.25</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="8"/>
+        <v>0.9375</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="9"/>
+        <v>0.5</v>
+      </c>
+      <c r="G25">
+        <f t="shared" ref="C25:I39" si="10">1-(($A25-$B$6)/G$4)^2</f>
+        <v>0.75</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="10"/>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="4"/>
+        <v>6.9767441860465115E-2</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="4"/>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="4"/>
+        <v>-2.1276595744680851E-2</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="4"/>
+        <v>-6.1224489795918366E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>23.5</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="6"/>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="7"/>
+        <v>0.5</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="8"/>
+        <v>0.75</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="10"/>
+        <v>-0.77777777777777768</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="10"/>
+        <v>-3</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="4"/>
+        <v>9.3023255813953487E-2</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="4"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="4"/>
+        <v>-4.0816326530612242E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="7"/>
+        <v>0.75</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="8"/>
+        <v>0.4375</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="9"/>
+        <v>1.5</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="10"/>
+        <v>-1.25</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="10"/>
+        <v>-3</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="4"/>
+        <v>0.11627906976744186</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="4"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="4"/>
+        <v>2.1276595744680851E-2</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="4"/>
+        <v>-2.0408163265306121E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>24.5</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="5"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="6"/>
+        <v>-0.77777777777777768</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="10"/>
+        <v>-3</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="10"/>
+        <v>-6.1111111111111107</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="10"/>
+        <v>-15</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="4"/>
+        <v>0.13953488372093023</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="4"/>
+        <v>8.8888888888888892E-2</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="4"/>
+        <v>4.2553191489361701E-2</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>25</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="6"/>
+        <v>-1.7777777777777781</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="7"/>
+        <v>1.25</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="8"/>
+        <v>-0.5625</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="9"/>
+        <v>2.5</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="10"/>
+        <v>-5.25</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="10"/>
+        <v>-10.111111111111112</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="10"/>
+        <v>-24</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="4"/>
+        <v>0.16279069767441862</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="4"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="4"/>
+        <v>6.3829787234042548E-2</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="4"/>
+        <v>2.0408163265306121E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>25.5</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="6"/>
+        <v>-3</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="7"/>
+        <v>1.5</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="8"/>
+        <v>-1.25</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="10"/>
+        <v>-8</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="10"/>
+        <v>-15</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="10"/>
+        <v>-35</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="4"/>
+        <v>0.18604651162790697</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="4"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="4"/>
+        <v>8.5106382978723402E-2</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="4"/>
+        <v>4.0816326530612242E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>26</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="5"/>
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="6"/>
+        <v>-4.4444444444444455</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="7"/>
+        <v>1.75</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="8"/>
+        <v>-2.0625</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="9"/>
+        <v>3.5</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="10"/>
+        <v>-11.25</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="10"/>
+        <v>-20.777777777777782</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="10"/>
+        <v>-48</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="4"/>
+        <v>0.20930232558139536</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="4"/>
+        <v>0.15555555555555556</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="4"/>
+        <v>0.10638297872340426</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="4"/>
+        <v>6.1224489795918366E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>26.5</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="5"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="6"/>
+        <v>-6.1111111111111107</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="8"/>
+        <v>-3</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="10"/>
+        <v>-15</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="10"/>
+        <v>-27.444444444444443</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="10"/>
+        <v>-63</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="4"/>
+        <v>0.23255813953488372</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="4"/>
+        <v>0.17777777777777778</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="4"/>
+        <v>0.1276595744680851</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="4"/>
+        <v>8.1632653061224483E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>27</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="6"/>
+        <v>-8</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="7"/>
+        <v>2.25</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="8"/>
+        <v>-4.0625</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="9"/>
+        <v>4.5</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="10"/>
+        <v>-19.25</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="10"/>
+        <v>-35</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="10"/>
+        <v>-80</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="4"/>
+        <v>0.2558139534883721</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="4"/>
+        <v>0.14893617021276595</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="4"/>
+        <v>0.10204081632653061</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>27.5</v>
+      </c>
+      <c r="B34">
+        <f t="shared" si="5"/>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="6"/>
+        <v>-10.111111111111112</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="7"/>
+        <v>2.5</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="8"/>
+        <v>-5.25</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="10"/>
+        <v>-24</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="10"/>
+        <v>-43.44444444444445</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="10"/>
+        <v>-99</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="4"/>
+        <v>0.27906976744186046</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="4"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="4"/>
+        <v>0.1702127659574468</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="4"/>
+        <v>0.12244897959183673</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>28</v>
+      </c>
+      <c r="B35">
+        <f t="shared" si="5"/>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="6"/>
+        <v>-12.444444444444443</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="7"/>
+        <v>2.75</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="8"/>
+        <v>-6.5625</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="9"/>
+        <v>5.5</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="10"/>
+        <v>-29.25</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="10"/>
+        <v>-52.777777777777771</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="10"/>
+        <v>-120</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="4"/>
+        <v>0.30232558139534882</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="4"/>
+        <v>0.24444444444444444</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="4"/>
+        <v>0.19148936170212766</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="4"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>28.5</v>
+      </c>
+      <c r="B36">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="6"/>
+        <v>-15</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="8"/>
+        <v>-8</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="9"/>
+        <v>6</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="10"/>
+        <v>-35</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="10"/>
+        <v>-63</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="10"/>
+        <v>-143</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="4"/>
+        <v>0.32558139534883723</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="4"/>
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="4"/>
+        <v>0.21276595744680851</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="4"/>
+        <v>0.16326530612244897</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>29</v>
+      </c>
+      <c r="B37">
+        <f t="shared" si="5"/>
+        <v>2.1666666666666665</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="6"/>
+        <v>-17.777777777777775</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="7"/>
+        <v>3.25</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="8"/>
+        <v>-9.5625</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="9"/>
+        <v>6.5</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="10"/>
+        <v>-41.25</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="10"/>
+        <v>-74.1111111111111</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="10"/>
+        <v>-168</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="4"/>
+        <v>0.34883720930232559</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="4"/>
+        <v>0.28888888888888886</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="4"/>
+        <v>0.23404255319148937</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="4"/>
+        <v>0.18367346938775511</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>29.5</v>
+      </c>
+      <c r="B38">
+        <f t="shared" si="5"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="6"/>
+        <v>-20.777777777777782</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="7"/>
+        <v>3.5</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="8"/>
+        <v>-11.25</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="10"/>
+        <v>-48</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="10"/>
+        <v>-86.111111111111128</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="10"/>
+        <v>-195</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="4"/>
+        <v>0.37209302325581395</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="4"/>
+        <v>0.31111111111111112</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="4"/>
+        <v>0.25531914893617019</v>
+      </c>
+      <c r="O38">
+        <f t="shared" si="4"/>
+        <v>0.20408163265306123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>30</v>
+      </c>
+      <c r="B39">
+        <f t="shared" si="5"/>
+        <v>2.5</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="6"/>
+        <v>-24</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="7"/>
+        <v>3.75</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="8"/>
+        <v>-13.0625</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="9"/>
+        <v>7.5</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="10"/>
+        <v>-55.25</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="10"/>
+        <v>-99</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="10"/>
+        <v>-224</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="4"/>
+        <v>0.39534883720930231</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="4"/>
+        <v>0.27659574468085107</v>
+      </c>
+      <c r="O39">
+        <f t="shared" si="4"/>
+        <v>0.22448979591836735</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BCDB501-68CB-41A2-9147-FB714368BD97}">
   <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9237,7 +11929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC026C63-00BE-41CB-A60E-94EB386A362C}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9520,7 +12212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C0A5B89-380D-4A9E-B2B1-12B37C9377C1}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/SRC/Controller/HVAC_controller/State_Reward_action defintion.xlsx
+++ b/SRC/Controller/HVAC_controller/State_Reward_action defintion.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YajuR\Desktop\Autonomy\Dwelling_simulator\SRC\Controller\HVAC_controller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC64148-1E05-4B38-BF2A-2F2E68A0D8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DA101E-25AF-4F1F-BF2A-34CFB0EB7CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2F0CEAD1-91A2-44EE-9519-226D71FD8C97}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{2F0CEAD1-91A2-44EE-9519-226D71FD8C97}"/>
   </bookViews>
   <sheets>
     <sheet name="Reward" sheetId="1" r:id="rId1"/>
     <sheet name="Reward Type 3" sheetId="3" r:id="rId2"/>
-    <sheet name="Reward Type 4" sheetId="6" r:id="rId3"/>
+    <sheet name="Reward TYpe 4" sheetId="7" r:id="rId3"/>
     <sheet name="Reward Type 2" sheetId="4" r:id="rId4"/>
     <sheet name="Rate change" sheetId="2" r:id="rId5"/>
     <sheet name="Boundary " sheetId="5" r:id="rId6"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="38">
   <si>
     <t xml:space="preserve">max </t>
   </si>
@@ -140,6 +140,21 @@
   </si>
   <si>
     <t>state - with band 3</t>
+  </si>
+  <si>
+    <t>Reward Type 5 - band 0.75</t>
+  </si>
+  <si>
+    <t>Reward Type 5 - band 1</t>
+  </si>
+  <si>
+    <t>Reward Type 5 - band 2</t>
+  </si>
+  <si>
+    <t>Reward Type 5 - band_3</t>
+  </si>
+  <si>
+    <t>Reward Type 5 -0.5</t>
   </si>
 </sst>
 </file>
@@ -3401,7 +3416,7 @@
           <c:yMode val="edge"/>
           <c:x val="1.1225338404246849E-2"/>
           <c:y val="0.91142535543763092"/>
-          <c:w val="0.69237552999132523"/>
+          <c:w val="0.97504223622638464"/>
           <c:h val="7.130344550915968E-2"/>
         </c:manualLayout>
       </c:layout>
@@ -3480,6 +3495,1915 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Reward TYpe 4'!$C$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Reward Type 5 - band_3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Reward TYpe 4'!$A$9:$A$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Reward TYpe 4'!$C$9:$C$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>-5.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4.4444444444444455</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.6944444444444438</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-2.3611111111111107</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1.7777777777777781</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-1.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.77777777777777768</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.36111111111111138</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.36111111111111138</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-0.77777777777777768</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-1.25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-1.7777777777777781</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-2.3611111111111107</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-3.6944444444444438</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-4.4444444444444455</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-5.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0540-44AC-A0D1-62ADB553A23F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Reward TYpe 4'!$E$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Reward Type 5 - band 2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Reward TYpe 4'!$A$9:$A$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Reward TYpe 4'!$E$9:$E$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>-13.0625</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-11.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-9.5625</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-6.5625</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-5.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4.0625</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-2.0625</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1.25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.5625</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-0.5625</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-1.25</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-2.0625</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-4.0625</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-5.25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-6.5625</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-8</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-9.5625</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-11.25</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-13.0625</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-0540-44AC-A0D1-62ADB553A23F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Reward TYpe 4'!$G$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Reward Type 5 - band 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Reward TYpe 4'!$A$9:$A$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Reward TYpe 4'!$G$9:$G$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>-55.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-41.25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-29.25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-24</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-19.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-15</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-11.25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-5.25</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1.25</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-1.25</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-5.25</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-8</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-11.25</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-15</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-19.25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-24</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-29.25</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-35</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-41.25</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-48</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-55.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-0540-44AC-A0D1-62ADB553A23F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="788353743"/>
+        <c:axId val="788356623"/>
+      </c:lineChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Reward TYpe 4'!$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>state - with band 3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Reward TYpe 4'!$A$9:$A$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Reward TYpe 4'!$B$9:$B$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>-2.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-2.3333333333333335</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-2.1666666666666665</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.8333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1.6666666666666667</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-1.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1.3333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-1.1666666666666667</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.83333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.66666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.66666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.83333333333333337</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.1666666666666667</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.3333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.6666666666666667</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.8333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.1666666666666665</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.3333333333333335</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0540-44AC-A0D1-62ADB553A23F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Reward TYpe 4'!$D$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>state - with band 2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:ln w="15875">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Reward TYpe 4'!$A$9:$A$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Reward TYpe 4'!$D$9:$D$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>-3.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-3.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-2.75</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-2.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-2.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-1.75</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1.25</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.75</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.25</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.75</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.75</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.25</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0540-44AC-A0D1-62ADB553A23F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Reward TYpe 4'!$F$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>state - with band 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Reward TYpe 4'!$A$9:$A$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>24.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Reward TYpe 4'!$F$9:$F$39</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>-7.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-6.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-5.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-3.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-2.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-0540-44AC-A0D1-62ADB553A23F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="696625343"/>
+        <c:axId val="696624863"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="788353743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IE"/>
+                  <a:t>T_in</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="788356623"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="788356623"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IE"/>
+                  <a:t>Reward</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="788353743"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="696624863"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-IE"/>
+                  <a:t>Normalized T_in [state]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="696625343"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="696625343"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="696624863"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:pattFill prst="ltDnDiag">
+          <a:fgClr>
+            <a:schemeClr val="dk1">
+              <a:lumMod val="15000"/>
+              <a:lumOff val="85000"/>
+            </a:schemeClr>
+          </a:fgClr>
+          <a:bgClr>
+            <a:schemeClr val="lt1"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4258,6 +6182,46 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5363,6 +7327,555 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="221">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="15875">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -5964,6 +8477,47 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>847725</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2203F8F-FFB5-3498-E58D-3869EF984122}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>452437</xdr:colOff>
       <xdr:row>5</xdr:row>
@@ -6320,6 +8874,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46252016-F883-43CE-A6F9-A6E9AB89863C}">
   <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="15.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -9580,7 +12137,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20B29F27-AD17-46E6-BD5E-59A5C1183A49}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2478197C-912F-49B1-B85B-33F45B916F22}">
   <dimension ref="A1:O39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9728,28 +12285,28 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
         <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
         <v>29</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I8" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L8">
         <v>21.5</v>
@@ -9773,15 +12330,15 @@
         <v>-2.5</v>
       </c>
       <c r="C9">
-        <f>1-(2*($A9-$B$6)/C$4)^2</f>
-        <v>-24</v>
+        <f>IF(ABS($A9-$B$6)&lt;C$4,1,1-(($A9-$B$6)/C$4)^2)</f>
+        <v>-5.25</v>
       </c>
       <c r="D9">
         <f>($A9-$E$3)/($E$4)</f>
         <v>-3.75</v>
       </c>
       <c r="E9">
-        <f>1-(($A9-$E$3)/E$4)^2</f>
+        <f>IF(ABS($A9-$B$6)&lt;E$4,1,1-(($A9-$B$6)/E$4)^2)</f>
         <v>-13.0625</v>
       </c>
       <c r="F9">
@@ -9789,31 +12346,31 @@
         <v>-7.5</v>
       </c>
       <c r="G9">
-        <f t="shared" ref="C9:I24" si="3">1-(($A9-$B$6)/G$4)^2</f>
+        <f>IF(ABS($A9-$B$6)&lt;G$4,1,1-(($A9-$B$6)/G$4)^2)</f>
         <v>-55.25</v>
       </c>
       <c r="H9">
-        <f t="shared" si="3"/>
+        <f>IF(ABS($A9-$B$6)&lt;H$4,1,1-(($A9-$B$6)/H$4)^2)</f>
         <v>-99</v>
       </c>
       <c r="I9">
-        <f t="shared" si="3"/>
+        <f>IF(ABS($A9-$B$6)&lt;I$4,1,1-(($A9-$B$6)/I$4)^2)</f>
         <v>-224</v>
       </c>
       <c r="L9">
-        <f t="shared" ref="L9:O39" si="4">($A9-L$8)/L$8</f>
+        <f t="shared" ref="L9:O39" si="3">($A9-L$8)/L$8</f>
         <v>-0.30232558139534882</v>
       </c>
       <c r="M9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.33333333333333331</v>
       </c>
       <c r="N9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.36170212765957449</v>
       </c>
       <c r="O9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.38775510204081631</v>
       </c>
     </row>
@@ -9822,51 +12379,51 @@
         <v>15.5</v>
       </c>
       <c r="B10">
-        <f t="shared" ref="B10:B39" si="5">(A10-AVERAGE(C$1:C$2))/$C$4</f>
+        <f t="shared" ref="B10:B39" si="4">(A10-AVERAGE(C$1:C$2))/$C$4</f>
         <v>-2.3333333333333335</v>
       </c>
       <c r="C10">
-        <f t="shared" ref="C10:C39" si="6">1-(2*($A10-$B$6)/C$4)^2</f>
-        <v>-20.777777777777782</v>
+        <f t="shared" ref="C10:C39" si="5">IF(ABS($A10-$B$6)&lt;C$4,1,1-(($A10-$B$6)/C$4)^2)</f>
+        <v>-4.4444444444444455</v>
       </c>
       <c r="D10">
-        <f t="shared" ref="D10:D39" si="7">($A10-$E$3)/($E$4)</f>
+        <f t="shared" ref="D10:D39" si="6">($A10-$E$3)/($E$4)</f>
         <v>-3.5</v>
       </c>
       <c r="E10">
-        <f t="shared" ref="E10:E39" si="8">1-(($A10-$E$3)/E$4)^2</f>
+        <f t="shared" ref="E10:I39" si="7">IF(ABS($A10-$B$6)&lt;E$4,1,1-(($A10-$B$6)/E$4)^2)</f>
         <v>-11.25</v>
       </c>
       <c r="F10">
-        <f t="shared" ref="F10:F39" si="9">($A10-$G$3)/($G$4)</f>
+        <f t="shared" ref="F10:F39" si="8">($A10-$G$3)/($G$4)</f>
         <v>-7</v>
       </c>
       <c r="G10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-48</v>
       </c>
       <c r="H10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-86.111111111111128</v>
       </c>
       <c r="I10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-195</v>
       </c>
       <c r="L10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.27906976744186046</v>
       </c>
       <c r="M10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.31111111111111112</v>
       </c>
       <c r="N10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.34042553191489361</v>
       </c>
       <c r="O10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.36734693877551022</v>
       </c>
     </row>
@@ -9875,51 +12432,51 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-2.1666666666666665</v>
       </c>
       <c r="C11">
+        <f t="shared" si="5"/>
+        <v>-3.6944444444444438</v>
+      </c>
+      <c r="D11">
         <f t="shared" si="6"/>
-        <v>-17.777777777777775</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="7"/>
         <v>-3.25</v>
       </c>
       <c r="E11">
+        <f t="shared" si="7"/>
+        <v>-9.5625</v>
+      </c>
+      <c r="F11">
         <f t="shared" si="8"/>
-        <v>-9.5625</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="9"/>
         <v>-6.5</v>
       </c>
       <c r="G11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-41.25</v>
       </c>
       <c r="H11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-74.1111111111111</v>
       </c>
       <c r="I11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-168</v>
       </c>
       <c r="L11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.2558139534883721</v>
       </c>
       <c r="M11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.28888888888888886</v>
       </c>
       <c r="N11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.31914893617021278</v>
       </c>
       <c r="O11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.34693877551020408</v>
       </c>
     </row>
@@ -9928,51 +12485,51 @@
         <v>16.5</v>
       </c>
       <c r="B12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-2</v>
       </c>
       <c r="C12">
+        <f t="shared" si="5"/>
+        <v>-3</v>
+      </c>
+      <c r="D12">
         <f t="shared" si="6"/>
-        <v>-15</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="7"/>
         <v>-3</v>
       </c>
       <c r="E12">
+        <f t="shared" si="7"/>
+        <v>-8</v>
+      </c>
+      <c r="F12">
         <f t="shared" si="8"/>
-        <v>-8</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="9"/>
         <v>-6</v>
       </c>
       <c r="G12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-35</v>
       </c>
       <c r="H12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-63</v>
       </c>
       <c r="I12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-143</v>
       </c>
       <c r="L12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.23255813953488372</v>
       </c>
       <c r="M12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.26666666666666666</v>
       </c>
       <c r="N12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.2978723404255319</v>
       </c>
       <c r="O12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.32653061224489793</v>
       </c>
     </row>
@@ -9981,51 +12538,51 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-1.8333333333333333</v>
       </c>
       <c r="C13">
+        <f t="shared" si="5"/>
+        <v>-2.3611111111111107</v>
+      </c>
+      <c r="D13">
         <f t="shared" si="6"/>
-        <v>-12.444444444444443</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="7"/>
         <v>-2.75</v>
       </c>
       <c r="E13">
+        <f t="shared" si="7"/>
+        <v>-6.5625</v>
+      </c>
+      <c r="F13">
         <f t="shared" si="8"/>
-        <v>-6.5625</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="9"/>
         <v>-5.5</v>
       </c>
       <c r="G13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-29.25</v>
       </c>
       <c r="H13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-52.777777777777771</v>
       </c>
       <c r="I13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-120</v>
       </c>
       <c r="L13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.20930232558139536</v>
       </c>
       <c r="M13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.24444444444444444</v>
       </c>
       <c r="N13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.27659574468085107</v>
       </c>
       <c r="O13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.30612244897959184</v>
       </c>
     </row>
@@ -10034,51 +12591,51 @@
         <v>17.5</v>
       </c>
       <c r="B14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-1.6666666666666667</v>
       </c>
       <c r="C14">
+        <f t="shared" si="5"/>
+        <v>-1.7777777777777781</v>
+      </c>
+      <c r="D14">
         <f t="shared" si="6"/>
-        <v>-10.111111111111112</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="7"/>
         <v>-2.5</v>
       </c>
       <c r="E14">
+        <f t="shared" si="7"/>
+        <v>-5.25</v>
+      </c>
+      <c r="F14">
         <f t="shared" si="8"/>
-        <v>-5.25</v>
-      </c>
-      <c r="F14">
-        <f t="shared" si="9"/>
         <v>-5</v>
       </c>
       <c r="G14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-24</v>
       </c>
       <c r="H14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-43.44444444444445</v>
       </c>
       <c r="I14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-99</v>
       </c>
       <c r="L14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.18604651162790697</v>
       </c>
       <c r="M14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.22222222222222221</v>
       </c>
       <c r="N14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.25531914893617019</v>
       </c>
       <c r="O14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.2857142857142857</v>
       </c>
     </row>
@@ -10087,51 +12644,51 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-1.5</v>
       </c>
       <c r="C15">
+        <f t="shared" si="5"/>
+        <v>-1.25</v>
+      </c>
+      <c r="D15">
         <f t="shared" si="6"/>
-        <v>-8</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="7"/>
         <v>-2.25</v>
       </c>
       <c r="E15">
+        <f t="shared" si="7"/>
+        <v>-4.0625</v>
+      </c>
+      <c r="F15">
         <f t="shared" si="8"/>
-        <v>-4.0625</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="9"/>
         <v>-4.5</v>
       </c>
       <c r="G15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-19.25</v>
       </c>
       <c r="H15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-35</v>
       </c>
       <c r="I15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-80</v>
       </c>
       <c r="L15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.16279069767441862</v>
       </c>
       <c r="M15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.2</v>
       </c>
       <c r="N15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.23404255319148937</v>
       </c>
       <c r="O15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.26530612244897961</v>
       </c>
     </row>
@@ -10140,51 +12697,51 @@
         <v>18.5</v>
       </c>
       <c r="B16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-1.3333333333333333</v>
       </c>
       <c r="C16">
+        <f t="shared" si="5"/>
+        <v>-0.77777777777777768</v>
+      </c>
+      <c r="D16">
         <f t="shared" si="6"/>
-        <v>-6.1111111111111107</v>
-      </c>
-      <c r="D16">
-        <f t="shared" si="7"/>
         <v>-2</v>
       </c>
       <c r="E16">
+        <f t="shared" si="7"/>
+        <v>-3</v>
+      </c>
+      <c r="F16">
         <f t="shared" si="8"/>
-        <v>-3</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="9"/>
         <v>-4</v>
       </c>
       <c r="G16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-15</v>
       </c>
       <c r="H16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-27.444444444444443</v>
       </c>
       <c r="I16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-63</v>
       </c>
       <c r="L16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.13953488372093023</v>
       </c>
       <c r="M16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.17777777777777778</v>
       </c>
       <c r="N16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.21276595744680851</v>
       </c>
       <c r="O16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.24489795918367346</v>
       </c>
     </row>
@@ -10193,51 +12750,51 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-1.1666666666666667</v>
       </c>
       <c r="C17">
+        <f t="shared" si="5"/>
+        <v>-0.36111111111111138</v>
+      </c>
+      <c r="D17">
         <f t="shared" si="6"/>
-        <v>-4.4444444444444455</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="7"/>
         <v>-1.75</v>
       </c>
       <c r="E17">
+        <f t="shared" si="7"/>
+        <v>-2.0625</v>
+      </c>
+      <c r="F17">
         <f t="shared" si="8"/>
-        <v>-2.0625</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="9"/>
         <v>-3.5</v>
       </c>
       <c r="G17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-11.25</v>
       </c>
       <c r="H17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-20.777777777777782</v>
       </c>
       <c r="I17">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-48</v>
       </c>
       <c r="L17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.11627906976744186</v>
       </c>
       <c r="M17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.15555555555555556</v>
       </c>
       <c r="N17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.19148936170212766</v>
       </c>
       <c r="O17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.22448979591836735</v>
       </c>
     </row>
@@ -10246,51 +12803,51 @@
         <v>19.5</v>
       </c>
       <c r="B18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-1</v>
       </c>
       <c r="C18">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D18">
         <f t="shared" si="6"/>
+        <v>-1.5</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="7"/>
+        <v>-1.25</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="8"/>
         <v>-3</v>
       </c>
-      <c r="D18">
-        <f t="shared" si="7"/>
-        <v>-1.5</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="8"/>
-        <v>-1.25</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="9"/>
-        <v>-3</v>
-      </c>
       <c r="G18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-8</v>
       </c>
       <c r="H18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-15</v>
       </c>
       <c r="I18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-35</v>
       </c>
       <c r="L18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-9.3023255813953487E-2</v>
       </c>
       <c r="M18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.13333333333333333</v>
       </c>
       <c r="N18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.1702127659574468</v>
       </c>
       <c r="O18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.20408163265306123</v>
       </c>
     </row>
@@ -10299,51 +12856,51 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-0.83333333333333337</v>
       </c>
       <c r="C19">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="D19">
         <f t="shared" si="6"/>
-        <v>-1.7777777777777781</v>
-      </c>
-      <c r="D19">
-        <f t="shared" si="7"/>
         <v>-1.25</v>
       </c>
       <c r="E19">
+        <f t="shared" si="7"/>
+        <v>-0.5625</v>
+      </c>
+      <c r="F19">
         <f t="shared" si="8"/>
-        <v>-0.5625</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="9"/>
         <v>-2.5</v>
       </c>
       <c r="G19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-5.25</v>
       </c>
       <c r="H19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-10.111111111111112</v>
       </c>
       <c r="I19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-24</v>
       </c>
       <c r="L19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-6.9767441860465115E-2</v>
       </c>
       <c r="M19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.1111111111111111</v>
       </c>
       <c r="N19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.14893617021276595</v>
       </c>
       <c r="O19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.18367346938775511</v>
       </c>
     </row>
@@ -10352,51 +12909,51 @@
         <v>20.5</v>
       </c>
       <c r="B20">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-0.66666666666666663</v>
       </c>
       <c r="C20">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="D20">
         <f t="shared" si="6"/>
-        <v>-0.77777777777777768</v>
-      </c>
-      <c r="D20">
-        <f t="shared" si="7"/>
         <v>-1</v>
       </c>
       <c r="E20">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F20">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="9"/>
         <v>-2</v>
       </c>
       <c r="G20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-3</v>
       </c>
       <c r="H20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-6.1111111111111107</v>
       </c>
       <c r="I20">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-15</v>
       </c>
       <c r="L20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-4.6511627906976744E-2</v>
       </c>
       <c r="M20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-8.8888888888888892E-2</v>
       </c>
       <c r="N20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.1276595744680851</v>
       </c>
       <c r="O20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.16326530612244897</v>
       </c>
     </row>
@@ -10405,51 +12962,51 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-0.5</v>
       </c>
       <c r="C21">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="D21">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <f t="shared" si="7"/>
         <v>-0.75</v>
       </c>
       <c r="E21">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F21">
         <f t="shared" si="8"/>
-        <v>0.4375</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="9"/>
         <v>-1.5</v>
       </c>
       <c r="G21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-1.25</v>
       </c>
       <c r="H21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-3</v>
       </c>
       <c r="I21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-8</v>
       </c>
       <c r="L21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-2.3255813953488372E-2</v>
       </c>
       <c r="M21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-6.6666666666666666E-2</v>
       </c>
       <c r="N21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.10638297872340426</v>
       </c>
       <c r="O21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.14285714285714285</v>
       </c>
     </row>
@@ -10458,51 +13015,51 @@
         <v>21.5</v>
       </c>
       <c r="B22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-0.33333333333333331</v>
       </c>
       <c r="C22">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="D22">
         <f t="shared" si="6"/>
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="D22">
-        <f t="shared" si="7"/>
         <v>-0.5</v>
       </c>
       <c r="E22">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
         <f t="shared" si="8"/>
-        <v>0.75</v>
-      </c>
-      <c r="F22" s="1">
-        <f t="shared" si="9"/>
         <v>-1</v>
       </c>
-      <c r="G22" s="1">
-        <f t="shared" si="3"/>
+      <c r="G22">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-0.77777777777777768</v>
       </c>
       <c r="I22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-3</v>
       </c>
       <c r="L22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-4.4444444444444446E-2</v>
       </c>
       <c r="N22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-8.5106382978723402E-2</v>
       </c>
       <c r="O22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.12244897959183673</v>
       </c>
     </row>
@@ -10511,51 +13068,51 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>-0.16666666666666666</v>
       </c>
       <c r="C23">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="D23">
         <f t="shared" si="6"/>
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="D23">
-        <f t="shared" si="7"/>
         <v>-0.25</v>
       </c>
       <c r="E23">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F23" s="1">
         <f t="shared" si="8"/>
-        <v>0.9375</v>
-      </c>
-      <c r="F23" s="1">
-        <f t="shared" si="9"/>
         <v>-0.5</v>
       </c>
-      <c r="G23" s="1">
-        <f t="shared" si="3"/>
-        <v>0.75</v>
+      <c r="G23">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="H23">
-        <f t="shared" si="3"/>
-        <v>0.55555555555555558</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="I23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.3255813953488372E-2</v>
       </c>
       <c r="M23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-2.2222222222222223E-2</v>
       </c>
       <c r="N23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-6.3829787234042548E-2</v>
       </c>
       <c r="O23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-0.10204081632653061</v>
       </c>
     </row>
@@ -10564,51 +13121,51 @@
         <v>22.5</v>
       </c>
       <c r="B24">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="F24" s="1">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="L24">
-        <f t="shared" si="4"/>
-        <v>4.6511627906976744E-2</v>
-      </c>
-      <c r="M24">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="C24">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="3"/>
+        <v>4.6511627906976744E-2</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="N24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-4.2553191489361701E-2</v>
       </c>
       <c r="O24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-8.1632653061224483E-2</v>
       </c>
     </row>
@@ -10617,51 +13174,51 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.16666666666666666</v>
       </c>
       <c r="C25">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="D25">
         <f t="shared" si="6"/>
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="7"/>
         <v>0.25</v>
       </c>
       <c r="E25">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F25">
         <f t="shared" si="8"/>
-        <v>0.9375</v>
-      </c>
-      <c r="F25">
-        <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
       <c r="G25">
-        <f t="shared" ref="C25:I39" si="10">1-(($A25-$B$6)/G$4)^2</f>
-        <v>0.75</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="H25">
-        <f t="shared" si="10"/>
-        <v>0.55555555555555558</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="I25">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>6.9767441860465115E-2</v>
       </c>
       <c r="M25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="N25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-2.1276595744680851E-2</v>
       </c>
       <c r="O25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-6.1224489795918366E-2</v>
       </c>
     </row>
@@ -10670,51 +13227,51 @@
         <v>23.5</v>
       </c>
       <c r="B26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="C26">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="D26">
         <f t="shared" si="6"/>
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
       <c r="E26">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F26">
         <f t="shared" si="8"/>
-        <v>0.75</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="G26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-0.77777777777777768</v>
       </c>
       <c r="I26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-3</v>
       </c>
       <c r="L26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>9.3023255813953487E-2</v>
       </c>
       <c r="M26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="N26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-4.0816326530612242E-2</v>
       </c>
     </row>
@@ -10723,51 +13280,51 @@
         <v>24</v>
       </c>
       <c r="B27">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="C27">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="D27">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <f t="shared" si="7"/>
         <v>0.75</v>
       </c>
       <c r="E27">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F27">
         <f t="shared" si="8"/>
-        <v>0.4375</v>
-      </c>
-      <c r="F27">
-        <f t="shared" si="9"/>
         <v>1.5</v>
       </c>
       <c r="G27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-1.25</v>
       </c>
       <c r="H27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-3</v>
       </c>
       <c r="I27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-8</v>
       </c>
       <c r="L27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.11627906976744186</v>
       </c>
       <c r="M27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="N27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1276595744680851E-2</v>
       </c>
       <c r="O27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>-2.0408163265306121E-2</v>
       </c>
     </row>
@@ -10776,51 +13333,51 @@
         <v>24.5</v>
       </c>
       <c r="B28">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="C28">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="D28">
         <f t="shared" si="6"/>
-        <v>-0.77777777777777768</v>
-      </c>
-      <c r="D28">
-        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E28">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F28">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="G28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-3</v>
       </c>
       <c r="H28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-6.1111111111111107</v>
       </c>
       <c r="I28">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-15</v>
       </c>
       <c r="L28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.13953488372093023</v>
       </c>
       <c r="M28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>8.8888888888888892E-2</v>
       </c>
       <c r="N28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>4.2553191489361701E-2</v>
       </c>
       <c r="O28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -10829,51 +13386,51 @@
         <v>25</v>
       </c>
       <c r="B29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.83333333333333337</v>
       </c>
       <c r="C29">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="D29">
         <f t="shared" si="6"/>
-        <v>-1.7777777777777781</v>
-      </c>
-      <c r="D29">
-        <f t="shared" si="7"/>
         <v>1.25</v>
       </c>
       <c r="E29">
+        <f t="shared" si="7"/>
+        <v>-0.5625</v>
+      </c>
+      <c r="F29">
         <f t="shared" si="8"/>
-        <v>-0.5625</v>
-      </c>
-      <c r="F29">
-        <f t="shared" si="9"/>
         <v>2.5</v>
       </c>
       <c r="G29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-5.25</v>
       </c>
       <c r="H29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-10.111111111111112</v>
       </c>
       <c r="I29">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-24</v>
       </c>
       <c r="L29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.16279069767441862</v>
       </c>
       <c r="M29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.1111111111111111</v>
       </c>
       <c r="N29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>6.3829787234042548E-2</v>
       </c>
       <c r="O29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.0408163265306121E-2</v>
       </c>
     </row>
@@ -10882,51 +13439,51 @@
         <v>25.5</v>
       </c>
       <c r="B30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="C30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D30">
         <f t="shared" si="6"/>
-        <v>-3</v>
-      </c>
-      <c r="D30">
-        <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
       <c r="E30">
+        <f t="shared" si="7"/>
+        <v>-1.25</v>
+      </c>
+      <c r="F30">
         <f t="shared" si="8"/>
-        <v>-1.25</v>
-      </c>
-      <c r="F30">
-        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="G30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-8</v>
       </c>
       <c r="H30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-15</v>
       </c>
       <c r="I30">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-35</v>
       </c>
       <c r="L30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.18604651162790697</v>
       </c>
       <c r="M30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.13333333333333333</v>
       </c>
       <c r="N30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>8.5106382978723402E-2</v>
       </c>
       <c r="O30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>4.0816326530612242E-2</v>
       </c>
     </row>
@@ -10935,51 +13492,51 @@
         <v>26</v>
       </c>
       <c r="B31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1.1666666666666667</v>
       </c>
       <c r="C31">
+        <f t="shared" si="5"/>
+        <v>-0.36111111111111138</v>
+      </c>
+      <c r="D31">
         <f t="shared" si="6"/>
-        <v>-4.4444444444444455</v>
-      </c>
-      <c r="D31">
-        <f t="shared" si="7"/>
         <v>1.75</v>
       </c>
       <c r="E31">
+        <f t="shared" si="7"/>
+        <v>-2.0625</v>
+      </c>
+      <c r="F31">
         <f t="shared" si="8"/>
-        <v>-2.0625</v>
-      </c>
-      <c r="F31">
-        <f t="shared" si="9"/>
         <v>3.5</v>
       </c>
       <c r="G31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-11.25</v>
       </c>
       <c r="H31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-20.777777777777782</v>
       </c>
       <c r="I31">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-48</v>
       </c>
       <c r="L31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.20930232558139536</v>
       </c>
       <c r="M31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.15555555555555556</v>
       </c>
       <c r="N31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.10638297872340426</v>
       </c>
       <c r="O31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>6.1224489795918366E-2</v>
       </c>
     </row>
@@ -10988,51 +13545,51 @@
         <v>26.5</v>
       </c>
       <c r="B32">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1.3333333333333333</v>
       </c>
       <c r="C32">
+        <f t="shared" si="5"/>
+        <v>-0.77777777777777768</v>
+      </c>
+      <c r="D32">
         <f t="shared" si="6"/>
-        <v>-6.1111111111111107</v>
-      </c>
-      <c r="D32">
-        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="E32">
+        <f t="shared" si="7"/>
+        <v>-3</v>
+      </c>
+      <c r="F32">
         <f t="shared" si="8"/>
-        <v>-3</v>
-      </c>
-      <c r="F32">
-        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="G32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-15</v>
       </c>
       <c r="H32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-27.444444444444443</v>
       </c>
       <c r="I32">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-63</v>
       </c>
       <c r="L32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.23255813953488372</v>
       </c>
       <c r="M32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.17777777777777778</v>
       </c>
       <c r="N32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.1276595744680851</v>
       </c>
       <c r="O32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>8.1632653061224483E-2</v>
       </c>
     </row>
@@ -11041,51 +13598,51 @@
         <v>27</v>
       </c>
       <c r="B33">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="C33">
+        <f t="shared" si="5"/>
+        <v>-1.25</v>
+      </c>
+      <c r="D33">
         <f t="shared" si="6"/>
-        <v>-8</v>
-      </c>
-      <c r="D33">
-        <f t="shared" si="7"/>
         <v>2.25</v>
       </c>
       <c r="E33">
+        <f t="shared" si="7"/>
+        <v>-4.0625</v>
+      </c>
+      <c r="F33">
         <f t="shared" si="8"/>
-        <v>-4.0625</v>
-      </c>
-      <c r="F33">
-        <f t="shared" si="9"/>
         <v>4.5</v>
       </c>
       <c r="G33">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-19.25</v>
       </c>
       <c r="H33">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-35</v>
       </c>
       <c r="I33">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-80</v>
       </c>
       <c r="L33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.2558139534883721</v>
       </c>
       <c r="M33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
       <c r="N33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.14893617021276595</v>
       </c>
       <c r="O33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.10204081632653061</v>
       </c>
     </row>
@@ -11094,51 +13651,51 @@
         <v>27.5</v>
       </c>
       <c r="B34">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1.6666666666666667</v>
       </c>
       <c r="C34">
+        <f t="shared" si="5"/>
+        <v>-1.7777777777777781</v>
+      </c>
+      <c r="D34">
         <f t="shared" si="6"/>
-        <v>-10.111111111111112</v>
-      </c>
-      <c r="D34">
-        <f t="shared" si="7"/>
         <v>2.5</v>
       </c>
       <c r="E34">
+        <f t="shared" si="7"/>
+        <v>-5.25</v>
+      </c>
+      <c r="F34">
         <f t="shared" si="8"/>
-        <v>-5.25</v>
-      </c>
-      <c r="F34">
-        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="G34">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-24</v>
       </c>
       <c r="H34">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-43.44444444444445</v>
       </c>
       <c r="I34">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-99</v>
       </c>
       <c r="L34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.27906976744186046</v>
       </c>
       <c r="M34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="N34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.1702127659574468</v>
       </c>
       <c r="O34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.12244897959183673</v>
       </c>
     </row>
@@ -11147,51 +13704,51 @@
         <v>28</v>
       </c>
       <c r="B35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1.8333333333333333</v>
       </c>
       <c r="C35">
+        <f t="shared" si="5"/>
+        <v>-2.3611111111111107</v>
+      </c>
+      <c r="D35">
         <f t="shared" si="6"/>
-        <v>-12.444444444444443</v>
-      </c>
-      <c r="D35">
-        <f t="shared" si="7"/>
         <v>2.75</v>
       </c>
       <c r="E35">
+        <f t="shared" si="7"/>
+        <v>-6.5625</v>
+      </c>
+      <c r="F35">
         <f t="shared" si="8"/>
-        <v>-6.5625</v>
-      </c>
-      <c r="F35">
-        <f t="shared" si="9"/>
         <v>5.5</v>
       </c>
       <c r="G35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-29.25</v>
       </c>
       <c r="H35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-52.777777777777771</v>
       </c>
       <c r="I35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-120</v>
       </c>
       <c r="L35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.30232558139534882</v>
       </c>
       <c r="M35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.24444444444444444</v>
       </c>
       <c r="N35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.19148936170212766</v>
       </c>
       <c r="O35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.14285714285714285</v>
       </c>
     </row>
@@ -11200,51 +13757,51 @@
         <v>28.5</v>
       </c>
       <c r="B36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="C36">
+        <f t="shared" si="5"/>
+        <v>-3</v>
+      </c>
+      <c r="D36">
         <f t="shared" si="6"/>
-        <v>-15</v>
-      </c>
-      <c r="D36">
-        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="E36">
+        <f t="shared" si="7"/>
+        <v>-8</v>
+      </c>
+      <c r="F36">
         <f t="shared" si="8"/>
-        <v>-8</v>
-      </c>
-      <c r="F36">
-        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="G36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-35</v>
       </c>
       <c r="H36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-63</v>
       </c>
       <c r="I36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-143</v>
       </c>
       <c r="L36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.32558139534883723</v>
       </c>
       <c r="M36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.26666666666666666</v>
       </c>
       <c r="N36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.21276595744680851</v>
       </c>
       <c r="O36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.16326530612244897</v>
       </c>
     </row>
@@ -11253,51 +13810,51 @@
         <v>29</v>
       </c>
       <c r="B37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.1666666666666665</v>
       </c>
       <c r="C37">
+        <f t="shared" si="5"/>
+        <v>-3.6944444444444438</v>
+      </c>
+      <c r="D37">
         <f t="shared" si="6"/>
-        <v>-17.777777777777775</v>
-      </c>
-      <c r="D37">
-        <f t="shared" si="7"/>
         <v>3.25</v>
       </c>
       <c r="E37">
+        <f t="shared" si="7"/>
+        <v>-9.5625</v>
+      </c>
+      <c r="F37">
         <f t="shared" si="8"/>
-        <v>-9.5625</v>
-      </c>
-      <c r="F37">
-        <f t="shared" si="9"/>
         <v>6.5</v>
       </c>
       <c r="G37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-41.25</v>
       </c>
       <c r="H37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-74.1111111111111</v>
       </c>
       <c r="I37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-168</v>
       </c>
       <c r="L37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.34883720930232559</v>
       </c>
       <c r="M37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.28888888888888886</v>
       </c>
       <c r="N37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.23404255319148937</v>
       </c>
       <c r="O37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.18367346938775511</v>
       </c>
     </row>
@@ -11306,51 +13863,51 @@
         <v>29.5</v>
       </c>
       <c r="B38">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.3333333333333335</v>
       </c>
       <c r="C38">
+        <f t="shared" si="5"/>
+        <v>-4.4444444444444455</v>
+      </c>
+      <c r="D38">
         <f t="shared" si="6"/>
-        <v>-20.777777777777782</v>
-      </c>
-      <c r="D38">
-        <f t="shared" si="7"/>
         <v>3.5</v>
       </c>
       <c r="E38">
+        <f t="shared" si="7"/>
+        <v>-11.25</v>
+      </c>
+      <c r="F38">
         <f t="shared" si="8"/>
-        <v>-11.25</v>
-      </c>
-      <c r="F38">
-        <f t="shared" si="9"/>
         <v>7</v>
       </c>
       <c r="G38">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-48</v>
       </c>
       <c r="H38">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-86.111111111111128</v>
       </c>
       <c r="I38">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-195</v>
       </c>
       <c r="L38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.37209302325581395</v>
       </c>
       <c r="M38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.31111111111111112</v>
       </c>
       <c r="N38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.25531914893617019</v>
       </c>
       <c r="O38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.20408163265306123</v>
       </c>
     </row>
@@ -11359,56 +13916,57 @@
         <v>30</v>
       </c>
       <c r="B39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>2.5</v>
       </c>
       <c r="C39">
+        <f t="shared" si="5"/>
+        <v>-5.25</v>
+      </c>
+      <c r="D39">
         <f t="shared" si="6"/>
-        <v>-24</v>
-      </c>
-      <c r="D39">
-        <f t="shared" si="7"/>
         <v>3.75</v>
       </c>
       <c r="E39">
+        <f t="shared" si="7"/>
+        <v>-13.0625</v>
+      </c>
+      <c r="F39">
         <f t="shared" si="8"/>
-        <v>-13.0625</v>
-      </c>
-      <c r="F39">
-        <f t="shared" si="9"/>
         <v>7.5</v>
       </c>
       <c r="G39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-55.25</v>
       </c>
       <c r="H39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-99</v>
       </c>
       <c r="I39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>-224</v>
       </c>
       <c r="L39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.39534883720930231</v>
       </c>
       <c r="M39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="N39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.27659574468085107</v>
       </c>
       <c r="O39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.22448979591836735</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11526,11 +14084,11 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <f t="shared" ref="B9:B39" si="0">(A9-AVERAGE(B$1:B$2))/(B$1-B$2)</f>
+        <f>(A9-AVERAGE(B$1:B$2))/(B$1-B$2)</f>
         <v>-1.25</v>
       </c>
       <c r="C9">
-        <f t="shared" ref="C9:C39" si="1">1-(A9-$B$6)^2/(B$1-B$2)</f>
+        <f t="shared" ref="C9:C39" si="0">1-(A9-$B$6)^2/(B$1-B$2)</f>
         <v>-8.375</v>
       </c>
     </row>
@@ -11539,11 +14097,11 @@
         <v>15.5</v>
       </c>
       <c r="B10">
+        <f t="shared" ref="B10:B39" si="1">(A10-AVERAGE(B$1:B$2))/(B$1-B$2)</f>
+        <v>-1.1666666666666667</v>
+      </c>
+      <c r="C10">
         <f t="shared" si="0"/>
-        <v>-1.1666666666666667</v>
-      </c>
-      <c r="C10">
-        <f t="shared" si="1"/>
         <v>-7.1666666666666661</v>
       </c>
     </row>
@@ -11552,11 +14110,11 @@
         <v>16</v>
       </c>
       <c r="B11">
+        <f t="shared" si="1"/>
+        <v>-1.0833333333333333</v>
+      </c>
+      <c r="C11">
         <f t="shared" si="0"/>
-        <v>-1.0833333333333333</v>
-      </c>
-      <c r="C11">
-        <f t="shared" si="1"/>
         <v>-6.041666666666667</v>
       </c>
     </row>
@@ -11565,11 +14123,11 @@
         <v>16.5</v>
       </c>
       <c r="B12">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="C12">
         <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-      <c r="C12">
-        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -11578,11 +14136,11 @@
         <v>17</v>
       </c>
       <c r="B13">
+        <f t="shared" si="1"/>
+        <v>-0.91666666666666663</v>
+      </c>
+      <c r="C13">
         <f t="shared" si="0"/>
-        <v>-0.91666666666666663</v>
-      </c>
-      <c r="C13">
-        <f t="shared" si="1"/>
         <v>-4.041666666666667</v>
       </c>
     </row>
@@ -11591,11 +14149,11 @@
         <v>17.5</v>
       </c>
       <c r="B14">
+        <f t="shared" si="1"/>
+        <v>-0.83333333333333337</v>
+      </c>
+      <c r="C14">
         <f t="shared" si="0"/>
-        <v>-0.83333333333333337</v>
-      </c>
-      <c r="C14">
-        <f t="shared" si="1"/>
         <v>-3.166666666666667</v>
       </c>
     </row>
@@ -11604,11 +14162,11 @@
         <v>18</v>
       </c>
       <c r="B15">
+        <f t="shared" si="1"/>
+        <v>-0.75</v>
+      </c>
+      <c r="C15">
         <f t="shared" si="0"/>
-        <v>-0.75</v>
-      </c>
-      <c r="C15">
-        <f t="shared" si="1"/>
         <v>-2.375</v>
       </c>
     </row>
@@ -11617,11 +14175,11 @@
         <v>18.5</v>
       </c>
       <c r="B16">
+        <f t="shared" si="1"/>
+        <v>-0.66666666666666663</v>
+      </c>
+      <c r="C16">
         <f t="shared" si="0"/>
-        <v>-0.66666666666666663</v>
-      </c>
-      <c r="C16">
-        <f t="shared" si="1"/>
         <v>-1.6666666666666665</v>
       </c>
     </row>
@@ -11630,11 +14188,11 @@
         <v>19</v>
       </c>
       <c r="B17">
+        <f t="shared" si="1"/>
+        <v>-0.58333333333333337</v>
+      </c>
+      <c r="C17">
         <f t="shared" si="0"/>
-        <v>-0.58333333333333337</v>
-      </c>
-      <c r="C17">
-        <f t="shared" si="1"/>
         <v>-1.0416666666666665</v>
       </c>
     </row>
@@ -11643,11 +14201,11 @@
         <v>19.5</v>
       </c>
       <c r="B18">
+        <f t="shared" si="1"/>
+        <v>-0.5</v>
+      </c>
+      <c r="C18">
         <f t="shared" si="0"/>
-        <v>-0.5</v>
-      </c>
-      <c r="C18">
-        <f t="shared" si="1"/>
         <v>-0.5</v>
       </c>
     </row>
@@ -11656,11 +14214,11 @@
         <v>20</v>
       </c>
       <c r="B19">
+        <f t="shared" si="1"/>
+        <v>-0.41666666666666669</v>
+      </c>
+      <c r="C19">
         <f t="shared" si="0"/>
-        <v>-0.41666666666666669</v>
-      </c>
-      <c r="C19">
-        <f t="shared" si="1"/>
         <v>-4.1666666666666741E-2</v>
       </c>
     </row>
@@ -11669,11 +14227,11 @@
         <v>20.5</v>
       </c>
       <c r="B20">
+        <f t="shared" si="1"/>
+        <v>-0.33333333333333331</v>
+      </c>
+      <c r="C20">
         <f t="shared" si="0"/>
-        <v>-0.33333333333333331</v>
-      </c>
-      <c r="C20">
-        <f t="shared" si="1"/>
         <v>0.33333333333333337</v>
       </c>
     </row>
@@ -11682,11 +14240,11 @@
         <v>21</v>
       </c>
       <c r="B21">
+        <f t="shared" si="1"/>
+        <v>-0.25</v>
+      </c>
+      <c r="C21">
         <f t="shared" si="0"/>
-        <v>-0.25</v>
-      </c>
-      <c r="C21">
-        <f t="shared" si="1"/>
         <v>0.625</v>
       </c>
     </row>
@@ -11695,11 +14253,11 @@
         <v>21.5</v>
       </c>
       <c r="B22">
+        <f t="shared" si="1"/>
+        <v>-0.16666666666666666</v>
+      </c>
+      <c r="C22">
         <f t="shared" si="0"/>
-        <v>-0.16666666666666666</v>
-      </c>
-      <c r="C22">
-        <f t="shared" si="1"/>
         <v>0.83333333333333337</v>
       </c>
     </row>
@@ -11708,11 +14266,11 @@
         <v>22</v>
       </c>
       <c r="B23">
+        <f t="shared" si="1"/>
+        <v>-8.3333333333333329E-2</v>
+      </c>
+      <c r="C23">
         <f t="shared" si="0"/>
-        <v>-8.3333333333333329E-2</v>
-      </c>
-      <c r="C23">
-        <f t="shared" si="1"/>
         <v>0.95833333333333337</v>
       </c>
     </row>
@@ -11721,11 +14279,11 @@
         <v>22.5</v>
       </c>
       <c r="B24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C24">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -11734,11 +14292,11 @@
         <v>23</v>
       </c>
       <c r="B25">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="C25">
         <f t="shared" si="0"/>
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="C25">
-        <f t="shared" si="1"/>
         <v>0.95833333333333337</v>
       </c>
     </row>
@@ -11747,11 +14305,11 @@
         <v>23.5</v>
       </c>
       <c r="B26">
+        <f t="shared" si="1"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C26">
         <f t="shared" si="0"/>
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="C26">
-        <f t="shared" si="1"/>
         <v>0.83333333333333337</v>
       </c>
     </row>
@@ -11760,11 +14318,11 @@
         <v>24</v>
       </c>
       <c r="B27">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="C27">
         <f t="shared" si="0"/>
-        <v>0.25</v>
-      </c>
-      <c r="C27">
-        <f t="shared" si="1"/>
         <v>0.625</v>
       </c>
     </row>
@@ -11773,11 +14331,11 @@
         <v>24.5</v>
       </c>
       <c r="B28">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C28">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C28">
-        <f t="shared" si="1"/>
         <v>0.33333333333333337</v>
       </c>
     </row>
@@ -11786,11 +14344,11 @@
         <v>25</v>
       </c>
       <c r="B29">
+        <f t="shared" si="1"/>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C29">
         <f t="shared" si="0"/>
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C29">
-        <f t="shared" si="1"/>
         <v>-4.1666666666666741E-2</v>
       </c>
     </row>
@@ -11799,11 +14357,11 @@
         <v>25.5</v>
       </c>
       <c r="B30">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="C30">
         <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="C30">
-        <f t="shared" si="1"/>
         <v>-0.5</v>
       </c>
     </row>
@@ -11812,11 +14370,11 @@
         <v>26</v>
       </c>
       <c r="B31">
+        <f t="shared" si="1"/>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C31">
         <f t="shared" si="0"/>
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="C31">
-        <f t="shared" si="1"/>
         <v>-1.0416666666666665</v>
       </c>
     </row>
@@ -11825,11 +14383,11 @@
         <v>26.5</v>
       </c>
       <c r="B32">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C32">
         <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="C32">
-        <f t="shared" si="1"/>
         <v>-1.6666666666666665</v>
       </c>
     </row>
@@ -11838,11 +14396,11 @@
         <v>27</v>
       </c>
       <c r="B33">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+      <c r="C33">
         <f t="shared" si="0"/>
-        <v>0.75</v>
-      </c>
-      <c r="C33">
-        <f t="shared" si="1"/>
         <v>-2.375</v>
       </c>
     </row>
@@ -11851,11 +14409,11 @@
         <v>27.5</v>
       </c>
       <c r="B34">
+        <f t="shared" si="1"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C34">
         <f t="shared" si="0"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="C34">
-        <f t="shared" si="1"/>
         <v>-3.166666666666667</v>
       </c>
     </row>
@@ -11864,11 +14422,11 @@
         <v>28</v>
       </c>
       <c r="B35">
+        <f t="shared" si="1"/>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C35">
         <f t="shared" si="0"/>
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="C35">
-        <f t="shared" si="1"/>
         <v>-4.041666666666667</v>
       </c>
     </row>
@@ -11877,11 +14435,11 @@
         <v>28.5</v>
       </c>
       <c r="B36">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C36">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C36">
-        <f t="shared" si="1"/>
         <v>-5</v>
       </c>
     </row>
@@ -11890,11 +14448,11 @@
         <v>29</v>
       </c>
       <c r="B37">
+        <f t="shared" si="1"/>
+        <v>1.0833333333333333</v>
+      </c>
+      <c r="C37">
         <f t="shared" si="0"/>
-        <v>1.0833333333333333</v>
-      </c>
-      <c r="C37">
-        <f t="shared" si="1"/>
         <v>-6.041666666666667</v>
       </c>
     </row>
@@ -11903,11 +14461,11 @@
         <v>29.5</v>
       </c>
       <c r="B38">
+        <f t="shared" si="1"/>
+        <v>1.1666666666666667</v>
+      </c>
+      <c r="C38">
         <f t="shared" si="0"/>
-        <v>1.1666666666666667</v>
-      </c>
-      <c r="C38">
-        <f t="shared" si="1"/>
         <v>-7.1666666666666661</v>
       </c>
     </row>
@@ -11916,11 +14474,11 @@
         <v>30</v>
       </c>
       <c r="B39">
+        <f t="shared" si="1"/>
+        <v>1.25</v>
+      </c>
+      <c r="C39">
         <f t="shared" si="0"/>
-        <v>1.25</v>
-      </c>
-      <c r="C39">
-        <f t="shared" si="1"/>
         <v>-8.375</v>
       </c>
     </row>

--- a/SRC/Controller/HVAC_controller/State_Reward_action defintion.xlsx
+++ b/SRC/Controller/HVAC_controller/State_Reward_action defintion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YajuR\Desktop\Autonomy\Dwelling_simulator\SRC\Controller\HVAC_controller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DA101E-25AF-4F1F-BF2A-34CFB0EB7CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907F1F1E-8D06-4C62-B89E-5B4A1149B438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{2F0CEAD1-91A2-44EE-9519-226D71FD8C97}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="14880" firstSheet="2" activeTab="2" xr2:uid="{2F0CEAD1-91A2-44EE-9519-226D71FD8C97}"/>
   </bookViews>
   <sheets>
     <sheet name="Reward" sheetId="1" r:id="rId1"/>
@@ -5304,6 +5304,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="696624863"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -13916,7 +13917,7 @@
         <v>30</v>
       </c>
       <c r="B39">
-        <f t="shared" si="4"/>
+        <f>(A39-AVERAGE(C$1:C$2))/$C$4</f>
         <v>2.5</v>
       </c>
       <c r="C39">
